--- a/knowledge/menu barbosa.xlsx
+++ b/knowledge/menu barbosa.xlsx
@@ -5,15 +5,23 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\DB\barbosa\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\GitHub\pizzeria-barbosa-v2\knowledge\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="18720" windowHeight="12405"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="18720" windowHeight="12405" firstSheet="1" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
-    <sheet name="Hoja2" sheetId="2" r:id="rId2"/>
+    <sheet name="Pizzas especialidades" sheetId="4" r:id="rId2"/>
+    <sheet name="Paquetes" sheetId="5" r:id="rId3"/>
+    <sheet name="Pizzas pollo y vegetarianas" sheetId="3" r:id="rId4"/>
+    <sheet name="Postres" sheetId="9" r:id="rId5"/>
+    <sheet name="A la Carta" sheetId="6" r:id="rId6"/>
+    <sheet name="Alitas" sheetId="8" r:id="rId7"/>
+    <sheet name="Bebidas" sheetId="7" r:id="rId8"/>
+    <sheet name="Extras" sheetId="10" r:id="rId9"/>
+    <sheet name="Hoja2" sheetId="2" r:id="rId10"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -25,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="674" uniqueCount="332">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1741" uniqueCount="374">
   <si>
     <t>Barbosa Mexicana</t>
   </si>
@@ -1021,13 +1029,139 @@
   </si>
   <si>
     <t>Pieza</t>
+  </si>
+  <si>
+    <t>Tamaño Pizzas con pollo</t>
+  </si>
+  <si>
+    <t>Tamaño Pizzas Vegetarianas</t>
+  </si>
+  <si>
+    <t>Lunes - Domingo</t>
+  </si>
+  <si>
+    <t>Tamaño Especial de la Casa</t>
+  </si>
+  <si>
+    <t>Tamaño Pizzas Especialidades</t>
+  </si>
+  <si>
+    <t>Valido en</t>
+  </si>
+  <si>
+    <t>Domicilio / Sucursal</t>
+  </si>
+  <si>
+    <t>Orden 7</t>
+  </si>
+  <si>
+    <t>Orden 10</t>
+  </si>
+  <si>
+    <t>Orden 14</t>
+  </si>
+  <si>
+    <t>Orden 20</t>
+  </si>
+  <si>
+    <t>Deditos de queso</t>
+  </si>
+  <si>
+    <t>Orilla de queso</t>
+  </si>
+  <si>
+    <t>Extra Pizzas especiales</t>
+  </si>
+  <si>
+    <t>Extra para Pizzas</t>
+  </si>
+  <si>
+    <t>Extra para Pastas</t>
+  </si>
+  <si>
+    <t>Platano</t>
+  </si>
+  <si>
+    <t>Durazno</t>
+  </si>
+  <si>
+    <t>Nuez</t>
+  </si>
+  <si>
+    <t>Galleta Oreo</t>
+  </si>
+  <si>
+    <t>Fresa</t>
+  </si>
+  <si>
+    <t>Extra Papas</t>
+  </si>
+  <si>
+    <t>Papas a la Francesa</t>
+  </si>
+  <si>
+    <t>6 Piezas</t>
+  </si>
+  <si>
+    <t>Chilli fries</t>
+  </si>
+  <si>
+    <t>Ferrero, Rompope, Capuchino, Vainilla, Chocoreta, Moka, Baileys, Mazapan, Gansito, Cajeta, Fresa, Chocolate Blanco, Oreo</t>
+  </si>
+  <si>
+    <t>No aplica</t>
+  </si>
+  <si>
+    <t>Dias Festivos</t>
+  </si>
+  <si>
+    <t>Sabores a Elegir</t>
+  </si>
+  <si>
+    <t>Alitas - 1 Sabor a Elegir</t>
+  </si>
+  <si>
+    <t>1 cheesesteak + papas + refresco chico</t>
+  </si>
+  <si>
+    <t>2 burritos + refresco chico</t>
+  </si>
+  <si>
+    <t>1 hamburguesa + papas + refresco chico</t>
+  </si>
+  <si>
+    <t>Rebanada de pizza + hot dog + refresco chico</t>
+  </si>
+  <si>
+    <t>2 hot dogs + refresco chico</t>
+  </si>
+  <si>
+    <t>Pizza grande + papas + refresco familiar (1.5L)</t>
+  </si>
+  <si>
+    <t>5 hamburguesas con papas + refresco familiar (1.5L)</t>
+  </si>
+  <si>
+    <t>Cuadrada (16 rebanadas) + papas a la francesa + refresco familiar (1.5L)</t>
+  </si>
+  <si>
+    <t>Cuadrada (16 rebanadas) + 10 alitas + papas a la francesa + refresco familiar (1.5L)</t>
+  </si>
+  <si>
+    <t>1 Mega (45x55 cm / 30 rebanadas) + 10 alitas + papas a la francesa + refresco familiar (1.5L)</t>
+  </si>
+  <si>
+    <t>Cuadrada (16 rebanadas) + papas a la francesa + refresco familiar (1.5L) + orden de 10 alitas</t>
+  </si>
+  <si>
+    <t>Grande (40cm / 8 rebanadas) + papas + refresco familiar (1.5L) + orden de 10 alitas</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1035,16 +1169,42 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor theme="4"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -1052,14 +1212,60 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </right>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </right>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Bueno" xfId="1" builtinId="26"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -1073,6 +1279,237 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="8" name="Tabla8" displayName="Tabla8" ref="B2:D16" totalsRowShown="0">
+  <autoFilter ref="B2:D16"/>
+  <tableColumns count="3">
+    <tableColumn id="1" name="Categoria"/>
+    <tableColumn id="2" name="Nombre"/>
+    <tableColumn id="3" name="Descripcion"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table10.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="Tabla6" displayName="Tabla6" ref="B23:D25" totalsRowShown="0">
+  <autoFilter ref="B23:D25"/>
+  <tableColumns count="3">
+    <tableColumn id="1" name="Categoria"/>
+    <tableColumn id="2" name="Nombre"/>
+    <tableColumn id="3" name="Descripcion"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table11.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="7" name="Tabla7" displayName="Tabla7" ref="F23:I25" totalsRowShown="0">
+  <autoFilter ref="F23:I25"/>
+  <tableColumns count="4">
+    <tableColumn id="1" name="Tamaño"/>
+    <tableColumn id="2" name="Precio"/>
+    <tableColumn id="3" name="Dias habiles"/>
+    <tableColumn id="4" name="Valido en"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table12.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Tabla1" displayName="Tabla1" ref="B2:J14" totalsRowShown="0" dataCellStyle="Normal">
+  <autoFilter ref="B2:J14"/>
+  <tableColumns count="9">
+    <tableColumn id="1" name="Categoria" dataCellStyle="Normal"/>
+    <tableColumn id="2" name="Nombre" dataCellStyle="Normal"/>
+    <tableColumn id="3" name="Descripcion" dataCellStyle="Normal"/>
+    <tableColumn id="4" name="Sabores" dataCellStyle="Normal"/>
+    <tableColumn id="5" name="Tamaño" dataCellStyle="Normal"/>
+    <tableColumn id="6" name="Precio" dataCellStyle="Normal"/>
+    <tableColumn id="7" name="Dias habiles" dataCellStyle="Normal"/>
+    <tableColumn id="8" name="Valido en" dataCellStyle="Normal"/>
+    <tableColumn id="9" name="Aplica Extra" dataCellStyle="Normal"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table13.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="14" name="Tabla14" displayName="Tabla14" ref="B2:J89" totalsRowShown="0">
+  <autoFilter ref="B2:J89"/>
+  <tableColumns count="9">
+    <tableColumn id="1" name="Categoria"/>
+    <tableColumn id="2" name="Nombre"/>
+    <tableColumn id="3" name="Descripcion"/>
+    <tableColumn id="4" name="Sabores"/>
+    <tableColumn id="5" name="Tamaño"/>
+    <tableColumn id="6" name="Precio"/>
+    <tableColumn id="7" name="Dias habiles"/>
+    <tableColumn id="8" name="Valido en"/>
+    <tableColumn id="9" name="Aplica Extra"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table14.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="18" name="Tabla18" displayName="Tabla18" ref="B2:K6" totalsRowShown="0">
+  <autoFilter ref="B2:K6"/>
+  <tableColumns count="10">
+    <tableColumn id="1" name="Categoria"/>
+    <tableColumn id="2" name="Nombre"/>
+    <tableColumn id="3" name="Descripcion"/>
+    <tableColumn id="4" name="Sabores"/>
+    <tableColumn id="5" name="Tamaño"/>
+    <tableColumn id="6" name="Precio"/>
+    <tableColumn id="7" name="Dias habiles"/>
+    <tableColumn id="8" name="Valido en"/>
+    <tableColumn id="9" name="Aplica Extra"/>
+    <tableColumn id="10" name="Tipo de Extra"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table15.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="19" name="Tabla19" displayName="Tabla19" ref="B2:K8" totalsRowShown="0">
+  <autoFilter ref="B2:K8"/>
+  <tableColumns count="10">
+    <tableColumn id="1" name="Categoria"/>
+    <tableColumn id="2" name="Nombre"/>
+    <tableColumn id="3" name="Descripcion"/>
+    <tableColumn id="4" name="Sabores"/>
+    <tableColumn id="5" name="Tamaño"/>
+    <tableColumn id="6" name="Precio"/>
+    <tableColumn id="7" name="Dias habiles"/>
+    <tableColumn id="8" name="Valido en"/>
+    <tableColumn id="9" name="Aplica Extra"/>
+    <tableColumn id="10" name="Tipo de Extra"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table16.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="20" name="Tabla20" displayName="Tabla20" ref="B2:E21" totalsRowShown="0">
+  <autoFilter ref="B2:E21"/>
+  <tableColumns count="4">
+    <tableColumn id="4" name="Categoria"/>
+    <tableColumn id="1" name="Extra Pizzas especiales"/>
+    <tableColumn id="2" name="Tamaño"/>
+    <tableColumn id="3" name="Precio"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="9" name="Tabla9" displayName="Tabla9" ref="F2:J9" totalsRowShown="0">
+  <autoFilter ref="F2:J9"/>
+  <tableColumns count="5">
+    <tableColumn id="1" name="Tamaño Pizzas Especialidades"/>
+    <tableColumn id="2" name="Precio"/>
+    <tableColumn id="3" name="Dias habiles"/>
+    <tableColumn id="4" name="Valido en"/>
+    <tableColumn id="5" name="Aplica Extra"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="10" name="Tabla10" displayName="Tabla10" ref="B20:D21" totalsRowShown="0">
+  <autoFilter ref="B20:D21"/>
+  <tableColumns count="3">
+    <tableColumn id="1" name="Categoria"/>
+    <tableColumn id="2" name="Nombre"/>
+    <tableColumn id="3" name="Descripcion"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="11" name="Tabla11" displayName="Tabla11" ref="F20:I26" totalsRowShown="0">
+  <autoFilter ref="F20:I26"/>
+  <tableColumns count="4">
+    <tableColumn id="1" name="Tamaño Especial de la Casa"/>
+    <tableColumn id="2" name="Precio"/>
+    <tableColumn id="3" name="Dias habiles"/>
+    <tableColumn id="4" name="Valido en"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="13" name="Tabla13" displayName="Tabla13" ref="B2:J14" totalsRowShown="0">
+  <autoFilter ref="B2:J14"/>
+  <tableColumns count="9">
+    <tableColumn id="1" name="Categoria"/>
+    <tableColumn id="2" name="Nombre"/>
+    <tableColumn id="3" name="Descripcion"/>
+    <tableColumn id="4" name="Tamaño"/>
+    <tableColumn id="5" name="Precio"/>
+    <tableColumn id="6" name="Dias habiles"/>
+    <tableColumn id="7" name="Valido en"/>
+    <tableColumn id="8" name="Dias Festivos"/>
+    <tableColumn id="9" name="Sabores a Elegir"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Tabla2" displayName="Tabla2" ref="B2:D11" totalsRowShown="0">
+  <autoFilter ref="B2:D11"/>
+  <tableColumns count="3">
+    <tableColumn id="1" name="Categoria"/>
+    <tableColumn id="2" name="Nombre"/>
+    <tableColumn id="3" name="Descripcion"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Tabla3" displayName="Tabla3" ref="F2:I9" totalsRowShown="0">
+  <autoFilter ref="F2:I9"/>
+  <tableColumns count="4">
+    <tableColumn id="1" name="Tamaño Pizzas con pollo"/>
+    <tableColumn id="2" name="Precio"/>
+    <tableColumn id="3" name="Dias habiles"/>
+    <tableColumn id="4" name="Valido en"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Tabla4" displayName="Tabla4" ref="B14:D17" totalsRowShown="0">
+  <autoFilter ref="B14:D17"/>
+  <tableColumns count="3">
+    <tableColumn id="1" name="Categoria"/>
+    <tableColumn id="2" name="Nombre"/>
+    <tableColumn id="3" name="Descripcion"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="Tabla5" displayName="Tabla5" ref="F14:I20" totalsRowShown="0">
+  <autoFilter ref="F14:I20"/>
+  <tableColumns count="4">
+    <tableColumn id="1" name="Tamaño Pizzas Vegetarianas"/>
+    <tableColumn id="2" name="Precio"/>
+    <tableColumn id="3" name="Dias habiles"/>
+    <tableColumn id="4" name="Valido en"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2640,1449 +3077,1600 @@
       </c>
     </row>
     <row r="108" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B108" t="s">
+      <c r="B108" s="6" t="s">
         <v>282</v>
       </c>
-      <c r="C108" t="s">
+      <c r="C108" s="6" t="s">
         <v>119</v>
       </c>
-      <c r="D108" t="s">
+      <c r="D108" s="6" t="s">
         <v>120</v>
       </c>
-      <c r="F108" t="s">
+      <c r="E108" s="6"/>
+      <c r="F108" s="6" t="s">
         <v>316</v>
       </c>
-      <c r="G108">
+      <c r="G108" s="6">
         <v>100</v>
       </c>
     </row>
     <row r="109" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B109" t="s">
+      <c r="B109" s="6" t="s">
         <v>282</v>
       </c>
-      <c r="C109" t="s">
+      <c r="C109" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="D109" t="s">
+      <c r="D109" s="6" t="s">
         <v>121</v>
       </c>
-      <c r="F109" t="s">
+      <c r="E109" s="6"/>
+      <c r="F109" s="6" t="s">
         <v>316</v>
       </c>
-      <c r="G109">
+      <c r="G109" s="6">
         <v>100</v>
       </c>
     </row>
     <row r="110" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B110" t="s">
+      <c r="B110" s="6" t="s">
         <v>282</v>
       </c>
-      <c r="C110" t="s">
+      <c r="C110" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="D110" t="s">
+      <c r="D110" s="6" t="s">
         <v>122</v>
       </c>
-      <c r="F110" t="s">
+      <c r="E110" s="6"/>
+      <c r="F110" s="6" t="s">
         <v>316</v>
       </c>
-      <c r="G110">
+      <c r="G110" s="6">
         <v>100</v>
       </c>
     </row>
     <row r="111" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B111" t="s">
+      <c r="B111" s="6" t="s">
         <v>282</v>
       </c>
-      <c r="C111" t="s">
+      <c r="C111" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="D111" t="s">
+      <c r="D111" s="6" t="s">
         <v>123</v>
       </c>
-      <c r="F111" t="s">
+      <c r="E111" s="6"/>
+      <c r="F111" s="6" t="s">
         <v>316</v>
       </c>
-      <c r="G111">
+      <c r="G111" s="6">
         <v>100</v>
       </c>
     </row>
     <row r="112" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B112" t="s">
+      <c r="B112" s="6" t="s">
         <v>282</v>
       </c>
-      <c r="C112" t="s">
+      <c r="C112" s="6" t="s">
         <v>124</v>
       </c>
-      <c r="D112" t="s">
+      <c r="D112" s="6" t="s">
         <v>125</v>
       </c>
-      <c r="F112" t="s">
+      <c r="E112" s="6"/>
+      <c r="F112" s="6" t="s">
         <v>316</v>
       </c>
-      <c r="G112">
+      <c r="G112" s="6">
         <v>100</v>
       </c>
     </row>
     <row r="113" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B113" t="s">
+      <c r="B113" s="6" t="s">
         <v>282</v>
       </c>
-      <c r="C113" t="s">
+      <c r="C113" s="6" t="s">
         <v>126</v>
       </c>
-      <c r="F113" t="s">
+      <c r="D113" s="6"/>
+      <c r="E113" s="6"/>
+      <c r="F113" s="6" t="s">
         <v>316</v>
       </c>
-      <c r="G113">
+      <c r="G113" s="6">
         <v>100</v>
       </c>
     </row>
     <row r="114" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B114" t="s">
+      <c r="B114" s="6" t="s">
         <v>282</v>
       </c>
-      <c r="C114" t="s">
+      <c r="C114" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="D114" t="s">
+      <c r="D114" s="6" t="s">
         <v>127</v>
       </c>
-      <c r="F114" t="s">
+      <c r="E114" s="6"/>
+      <c r="F114" s="6" t="s">
         <v>316</v>
       </c>
-      <c r="G114">
+      <c r="G114" s="6">
         <v>110</v>
       </c>
     </row>
+    <row r="115" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B115" s="6"/>
+      <c r="C115" s="6"/>
+      <c r="D115" s="6"/>
+      <c r="E115" s="6"/>
+      <c r="F115" s="6"/>
+      <c r="G115" s="6"/>
+    </row>
     <row r="116" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B116" t="s">
+      <c r="B116" s="6" t="s">
         <v>128</v>
       </c>
-      <c r="C116" t="s">
+      <c r="C116" s="6" t="s">
         <v>131</v>
       </c>
-      <c r="D116" t="s">
+      <c r="D116" s="6" t="s">
         <v>129</v>
       </c>
-      <c r="F116" t="s">
+      <c r="E116" s="6"/>
+      <c r="F116" s="6" t="s">
         <v>316</v>
       </c>
-      <c r="G116">
+      <c r="G116" s="6">
         <v>105</v>
       </c>
     </row>
     <row r="117" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B117" t="s">
+      <c r="B117" s="6" t="s">
         <v>128</v>
       </c>
-      <c r="C117" t="s">
+      <c r="C117" s="6" t="s">
         <v>130</v>
       </c>
-      <c r="D117" t="s">
+      <c r="D117" s="6" t="s">
         <v>129</v>
       </c>
-      <c r="F117" t="s">
+      <c r="E117" s="6"/>
+      <c r="F117" s="6" t="s">
         <v>316</v>
       </c>
-      <c r="G117">
+      <c r="G117" s="6">
         <v>105</v>
       </c>
     </row>
     <row r="118" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B118" t="s">
+      <c r="B118" s="6" t="s">
         <v>128</v>
       </c>
-      <c r="C118" t="s">
+      <c r="C118" s="6" t="s">
         <v>132</v>
       </c>
-      <c r="D118" t="s">
+      <c r="D118" s="6" t="s">
         <v>133</v>
       </c>
-      <c r="F118" t="s">
+      <c r="E118" s="6"/>
+      <c r="F118" s="6" t="s">
         <v>316</v>
       </c>
-      <c r="G118">
+      <c r="G118" s="6">
         <v>105</v>
       </c>
     </row>
     <row r="119" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B119" t="s">
+      <c r="B119" s="6" t="s">
         <v>128</v>
       </c>
-      <c r="C119" t="s">
+      <c r="C119" s="6" t="s">
         <v>134</v>
       </c>
-      <c r="D119" t="s">
+      <c r="D119" s="6" t="s">
         <v>135</v>
       </c>
-      <c r="F119" t="s">
+      <c r="E119" s="6"/>
+      <c r="F119" s="6" t="s">
         <v>316</v>
       </c>
-      <c r="G119">
+      <c r="G119" s="6">
         <v>105</v>
       </c>
     </row>
     <row r="120" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B120" t="s">
+      <c r="B120" s="6" t="s">
         <v>128</v>
       </c>
-      <c r="C120" t="s">
+      <c r="C120" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="D120" t="s">
+      <c r="D120" s="6" t="s">
         <v>136</v>
       </c>
-      <c r="F120" t="s">
+      <c r="E120" s="6"/>
+      <c r="F120" s="6" t="s">
         <v>316</v>
       </c>
-      <c r="G120">
+      <c r="G120" s="6">
         <v>105</v>
       </c>
     </row>
     <row r="121" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B121" t="s">
+      <c r="B121" s="6" t="s">
         <v>128</v>
       </c>
-      <c r="C121" t="s">
+      <c r="C121" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="D121" t="s">
+      <c r="D121" s="6" t="s">
         <v>137</v>
       </c>
-      <c r="F121" t="s">
+      <c r="E121" s="6"/>
+      <c r="F121" s="6" t="s">
         <v>316</v>
       </c>
-      <c r="G121">
+      <c r="G121" s="6">
         <v>105</v>
       </c>
     </row>
+    <row r="122" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B122" s="6"/>
+      <c r="C122" s="6"/>
+      <c r="D122" s="6"/>
+      <c r="E122" s="6"/>
+      <c r="F122" s="6"/>
+      <c r="G122" s="6"/>
+    </row>
     <row r="123" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B123" t="s">
+      <c r="B123" s="6" t="s">
         <v>138</v>
       </c>
-      <c r="C123" t="s">
+      <c r="C123" s="6" t="s">
         <v>139</v>
       </c>
-      <c r="D123" t="s">
+      <c r="D123" s="6" t="s">
         <v>140</v>
       </c>
-      <c r="F123" t="s">
+      <c r="E123" s="6"/>
+      <c r="F123" s="6" t="s">
         <v>316</v>
       </c>
-      <c r="G123">
+      <c r="G123" s="6">
         <v>95</v>
       </c>
     </row>
     <row r="124" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B124" t="s">
+      <c r="B124" s="6" t="s">
         <v>138</v>
       </c>
-      <c r="C124" t="s">
+      <c r="C124" s="6" t="s">
         <v>141</v>
       </c>
-      <c r="D124" t="s">
+      <c r="D124" s="6" t="s">
         <v>142</v>
       </c>
-      <c r="F124" t="s">
+      <c r="E124" s="6"/>
+      <c r="F124" s="6" t="s">
         <v>316</v>
       </c>
-      <c r="G124">
+      <c r="G124" s="6">
         <v>85</v>
       </c>
     </row>
+    <row r="125" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B125" s="6"/>
+      <c r="C125" s="6"/>
+      <c r="D125" s="6"/>
+      <c r="E125" s="6"/>
+      <c r="F125" s="6"/>
+      <c r="G125" s="6"/>
+    </row>
     <row r="126" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B126" t="s">
+      <c r="B126" s="6" t="s">
         <v>209</v>
       </c>
-      <c r="C126" t="s">
+      <c r="C126" s="6" t="s">
         <v>210</v>
       </c>
-      <c r="D126" t="s">
+      <c r="D126" s="6" t="s">
         <v>211</v>
       </c>
-      <c r="F126" t="s">
+      <c r="E126" s="6"/>
+      <c r="F126" s="6" t="s">
         <v>316</v>
       </c>
-      <c r="G126">
+      <c r="G126" s="6">
         <v>100</v>
       </c>
     </row>
     <row r="127" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B127" t="s">
+      <c r="B127" s="6" t="s">
         <v>209</v>
       </c>
-      <c r="C127" t="s">
+      <c r="C127" s="6" t="s">
         <v>212</v>
       </c>
-      <c r="D127" t="s">
+      <c r="D127" s="6" t="s">
         <v>213</v>
       </c>
-      <c r="F127" t="s">
+      <c r="E127" s="6"/>
+      <c r="F127" s="6" t="s">
         <v>316</v>
       </c>
-      <c r="G127">
+      <c r="G127" s="6">
         <v>100</v>
       </c>
     </row>
     <row r="128" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B128" t="s">
+      <c r="B128" s="6" t="s">
         <v>209</v>
       </c>
-      <c r="C128" t="s">
+      <c r="C128" s="6" t="s">
         <v>214</v>
       </c>
-      <c r="D128" t="s">
+      <c r="D128" s="6" t="s">
         <v>215</v>
       </c>
-      <c r="F128" t="s">
+      <c r="E128" s="6"/>
+      <c r="F128" s="6" t="s">
         <v>316</v>
       </c>
-      <c r="G128">
+      <c r="G128" s="6">
         <v>100</v>
       </c>
     </row>
     <row r="129" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B129" t="s">
+      <c r="B129" s="6" t="s">
         <v>209</v>
       </c>
-      <c r="C129" t="s">
+      <c r="C129" s="6" t="s">
         <v>216</v>
       </c>
-      <c r="D129" t="s">
+      <c r="D129" s="6" t="s">
         <v>217</v>
       </c>
-      <c r="F129" t="s">
+      <c r="E129" s="6"/>
+      <c r="F129" s="6" t="s">
         <v>316</v>
       </c>
-      <c r="G129">
+      <c r="G129" s="6">
         <v>100</v>
       </c>
     </row>
     <row r="130" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B130" t="s">
+      <c r="B130" s="6" t="s">
         <v>209</v>
       </c>
-      <c r="C130" t="s">
+      <c r="C130" s="6" t="s">
         <v>218</v>
       </c>
-      <c r="D130" t="s">
+      <c r="D130" s="6" t="s">
         <v>219</v>
       </c>
-      <c r="F130" t="s">
+      <c r="E130" s="6"/>
+      <c r="F130" s="6" t="s">
         <v>316</v>
       </c>
-      <c r="G130">
+      <c r="G130" s="6">
         <v>100</v>
       </c>
     </row>
     <row r="132" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B132" t="s">
+      <c r="B132" s="6" t="s">
         <v>153</v>
       </c>
-      <c r="C132" t="s">
+      <c r="C132" s="6" t="s">
         <v>311</v>
       </c>
-      <c r="D132" t="s">
+      <c r="D132" s="6" t="s">
         <v>143</v>
       </c>
-      <c r="F132" t="s">
-        <v>281</v>
-      </c>
-      <c r="G132">
+      <c r="E132" s="6"/>
+      <c r="F132" s="6" t="s">
+        <v>281</v>
+      </c>
+      <c r="G132" s="6">
         <v>140</v>
       </c>
-      <c r="J132" t="s">
+      <c r="H132" s="6"/>
+      <c r="I132" s="6"/>
+      <c r="J132" s="6" t="s">
         <v>327</v>
       </c>
-      <c r="K132" t="s">
+      <c r="K132" s="6" t="s">
         <v>148</v>
       </c>
     </row>
     <row r="133" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B133" t="s">
+      <c r="B133" s="6" t="s">
         <v>153</v>
       </c>
-      <c r="C133" t="s">
+      <c r="C133" s="6" t="s">
         <v>312</v>
       </c>
-      <c r="D133" t="s">
+      <c r="D133" s="6" t="s">
         <v>144</v>
       </c>
-      <c r="F133" t="s">
-        <v>281</v>
-      </c>
-      <c r="G133">
+      <c r="E133" s="6"/>
+      <c r="F133" s="6" t="s">
+        <v>281</v>
+      </c>
+      <c r="G133" s="6">
         <v>140</v>
       </c>
-      <c r="J133" t="s">
+      <c r="H133" s="6"/>
+      <c r="I133" s="6"/>
+      <c r="J133" s="6" t="s">
         <v>327</v>
       </c>
-      <c r="K133" t="s">
+      <c r="K133" s="6" t="s">
         <v>148</v>
       </c>
     </row>
     <row r="134" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B134" t="s">
+      <c r="B134" s="6" t="s">
         <v>153</v>
       </c>
-      <c r="C134" t="s">
+      <c r="C134" s="6" t="s">
         <v>312</v>
       </c>
-      <c r="D134" t="s">
+      <c r="D134" s="6" t="s">
         <v>145</v>
       </c>
-      <c r="F134" t="s">
-        <v>281</v>
-      </c>
-      <c r="G134">
+      <c r="E134" s="6"/>
+      <c r="F134" s="6" t="s">
+        <v>281</v>
+      </c>
+      <c r="G134" s="6">
         <v>180</v>
       </c>
-      <c r="J134" t="s">
+      <c r="H134" s="6"/>
+      <c r="I134" s="6"/>
+      <c r="J134" s="6" t="s">
         <v>327</v>
       </c>
-      <c r="K134" t="s">
+      <c r="K134" s="6" t="s">
         <v>148</v>
       </c>
     </row>
     <row r="135" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B135" t="s">
+      <c r="B135" s="6" t="s">
         <v>153</v>
       </c>
-      <c r="C135" t="s">
+      <c r="C135" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="F135" t="s">
-        <v>281</v>
-      </c>
-      <c r="G135">
+      <c r="D135" s="6"/>
+      <c r="E135" s="6"/>
+      <c r="F135" s="6" t="s">
+        <v>281</v>
+      </c>
+      <c r="G135" s="6">
         <v>140</v>
       </c>
-      <c r="J135" t="s">
+      <c r="H135" s="6"/>
+      <c r="I135" s="6"/>
+      <c r="J135" s="6" t="s">
         <v>327</v>
       </c>
-      <c r="K135" t="s">
+      <c r="K135" s="6" t="s">
         <v>148</v>
       </c>
     </row>
     <row r="136" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B136" t="s">
+      <c r="B136" s="6" t="s">
         <v>153</v>
       </c>
-      <c r="C136" t="s">
+      <c r="C136" s="6" t="s">
         <v>313</v>
       </c>
-      <c r="D136" t="s">
+      <c r="D136" s="6" t="s">
         <v>144</v>
       </c>
-      <c r="F136" t="s">
-        <v>281</v>
-      </c>
-      <c r="G136">
+      <c r="E136" s="6"/>
+      <c r="F136" s="6" t="s">
+        <v>281</v>
+      </c>
+      <c r="G136" s="6">
         <v>140</v>
       </c>
-      <c r="J136" t="s">
+      <c r="H136" s="6"/>
+      <c r="I136" s="6"/>
+      <c r="J136" s="6" t="s">
         <v>327</v>
       </c>
-      <c r="K136" t="s">
+      <c r="K136" s="6" t="s">
         <v>148</v>
       </c>
     </row>
     <row r="137" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B137" t="s">
+      <c r="B137" s="6" t="s">
         <v>153</v>
       </c>
-      <c r="C137" t="s">
+      <c r="C137" s="6" t="s">
         <v>313</v>
       </c>
-      <c r="D137" t="s">
+      <c r="D137" s="6" t="s">
         <v>145</v>
       </c>
-      <c r="F137" t="s">
-        <v>281</v>
-      </c>
-      <c r="G137">
+      <c r="E137" s="6"/>
+      <c r="F137" s="6" t="s">
+        <v>281</v>
+      </c>
+      <c r="G137" s="6">
         <v>180</v>
       </c>
-      <c r="J137" t="s">
+      <c r="H137" s="6"/>
+      <c r="I137" s="6"/>
+      <c r="J137" s="6" t="s">
         <v>327</v>
       </c>
-      <c r="K137" t="s">
+      <c r="K137" s="6" t="s">
         <v>148</v>
       </c>
     </row>
     <row r="138" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B138" t="s">
+      <c r="B138" s="6" t="s">
         <v>153</v>
       </c>
-      <c r="C138" t="s">
+      <c r="C138" s="6" t="s">
         <v>147</v>
       </c>
-      <c r="F138" t="s">
-        <v>281</v>
-      </c>
-      <c r="G138">
+      <c r="D138" s="6"/>
+      <c r="E138" s="6"/>
+      <c r="F138" s="6" t="s">
+        <v>281</v>
+      </c>
+      <c r="G138" s="6">
         <v>140</v>
       </c>
-      <c r="J138" t="s">
+      <c r="H138" s="6"/>
+      <c r="I138" s="6"/>
+      <c r="J138" s="6" t="s">
         <v>327</v>
       </c>
-      <c r="K138" t="s">
+      <c r="K138" s="6" t="s">
         <v>148</v>
       </c>
     </row>
     <row r="139" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B139" t="s">
+      <c r="B139" s="6" t="s">
         <v>314</v>
       </c>
-      <c r="C139" t="s">
+      <c r="C139" s="6" t="s">
         <v>150</v>
       </c>
-      <c r="D139" t="s">
+      <c r="D139" s="6" t="s">
         <v>151</v>
       </c>
-      <c r="F139" t="s">
-        <v>281</v>
-      </c>
-      <c r="G139">
+      <c r="E139" s="6"/>
+      <c r="F139" s="6" t="s">
+        <v>281</v>
+      </c>
+      <c r="G139" s="6">
         <v>130</v>
       </c>
-      <c r="J139" t="s">
+      <c r="H139" s="6"/>
+      <c r="I139" s="6"/>
+      <c r="J139" s="6" t="s">
         <v>327</v>
       </c>
-      <c r="K139" t="s">
+      <c r="K139" s="6" t="s">
         <v>148</v>
       </c>
     </row>
     <row r="142" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B142" t="s">
+      <c r="B142" s="6" t="s">
         <v>152</v>
       </c>
-      <c r="C142" t="s">
+      <c r="C142" s="6" t="s">
         <v>154</v>
       </c>
-      <c r="D142" t="s">
+      <c r="D142" s="6" t="s">
         <v>155</v>
       </c>
-      <c r="F142" t="s">
-        <v>281</v>
-      </c>
-      <c r="G142">
+      <c r="E142" s="6"/>
+      <c r="F142" s="6" t="s">
+        <v>281</v>
+      </c>
+      <c r="G142" s="6">
         <v>110</v>
       </c>
     </row>
     <row r="143" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B143" t="s">
+      <c r="B143" s="6" t="s">
         <v>152</v>
       </c>
-      <c r="C143" t="s">
+      <c r="C143" s="6" t="s">
         <v>156</v>
       </c>
-      <c r="D143" t="s">
+      <c r="D143" s="6" t="s">
         <v>157</v>
       </c>
-      <c r="F143" t="s">
-        <v>281</v>
-      </c>
-      <c r="G143">
+      <c r="E143" s="6"/>
+      <c r="F143" s="6" t="s">
+        <v>281</v>
+      </c>
+      <c r="G143" s="6">
         <v>110</v>
       </c>
     </row>
     <row r="144" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B144" t="s">
+      <c r="B144" s="6" t="s">
         <v>152</v>
       </c>
-      <c r="C144" t="s">
+      <c r="C144" s="6" t="s">
         <v>158</v>
       </c>
-      <c r="D144" t="s">
+      <c r="D144" s="6" t="s">
         <v>160</v>
       </c>
-      <c r="F144" t="s">
-        <v>281</v>
-      </c>
-      <c r="G144">
+      <c r="E144" s="6"/>
+      <c r="F144" s="6" t="s">
+        <v>281</v>
+      </c>
+      <c r="G144" s="6">
         <v>120</v>
       </c>
     </row>
     <row r="145" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B145" t="s">
+      <c r="B145" s="6" t="s">
         <v>152</v>
       </c>
-      <c r="C145" t="s">
+      <c r="C145" s="6" t="s">
         <v>159</v>
       </c>
-      <c r="D145" t="s">
+      <c r="D145" s="6" t="s">
         <v>161</v>
       </c>
-      <c r="F145" t="s">
-        <v>281</v>
-      </c>
-      <c r="G145">
+      <c r="E145" s="6"/>
+      <c r="F145" s="6" t="s">
+        <v>281</v>
+      </c>
+      <c r="G145" s="6">
         <v>120</v>
       </c>
     </row>
     <row r="146" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B146" t="s">
+      <c r="B146" s="6" t="s">
         <v>152</v>
       </c>
-      <c r="C146" t="s">
+      <c r="C146" s="6" t="s">
         <v>162</v>
       </c>
-      <c r="D146" t="s">
+      <c r="D146" s="6" t="s">
         <v>163</v>
       </c>
-      <c r="F146" t="s">
-        <v>281</v>
-      </c>
-      <c r="G146">
+      <c r="E146" s="6"/>
+      <c r="F146" s="6" t="s">
+        <v>281</v>
+      </c>
+      <c r="G146" s="6">
         <v>120</v>
       </c>
     </row>
     <row r="147" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B147" t="s">
+      <c r="B147" s="6" t="s">
         <v>152</v>
       </c>
-      <c r="C147" t="s">
+      <c r="C147" s="6" t="s">
         <v>164</v>
       </c>
-      <c r="D147" t="s">
+      <c r="D147" s="6" t="s">
         <v>165</v>
       </c>
-      <c r="F147" t="s">
-        <v>281</v>
-      </c>
-      <c r="G147">
+      <c r="E147" s="6"/>
+      <c r="F147" s="6" t="s">
+        <v>281</v>
+      </c>
+      <c r="G147" s="6">
         <v>120</v>
       </c>
     </row>
     <row r="149" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B149" t="s">
+      <c r="B149" s="6" t="s">
         <v>166</v>
       </c>
-      <c r="C149" t="s">
+      <c r="C149" s="6" t="s">
         <v>167</v>
       </c>
-      <c r="E149" t="s">
+      <c r="D149" s="6"/>
+      <c r="E149" s="6" t="s">
         <v>283</v>
       </c>
-      <c r="F149" t="s">
-        <v>281</v>
-      </c>
-      <c r="G149">
+      <c r="F149" s="6" t="s">
+        <v>281</v>
+      </c>
+      <c r="G149" s="6">
         <v>45</v>
       </c>
-      <c r="J149" t="s">
+      <c r="H149" s="6"/>
+      <c r="I149" s="6"/>
+      <c r="J149" s="6" t="s">
         <v>327</v>
       </c>
-      <c r="K149" t="s">
+      <c r="K149" s="6" t="s">
         <v>169</v>
       </c>
     </row>
     <row r="152" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B152" t="s">
+      <c r="B152" s="6" t="s">
         <v>170</v>
       </c>
-      <c r="C152" t="s">
+      <c r="C152" s="6" t="s">
         <v>171</v>
       </c>
-      <c r="D152" t="s">
+      <c r="D152" s="6" t="s">
         <v>172</v>
       </c>
-      <c r="F152" t="s">
-        <v>281</v>
-      </c>
-      <c r="G152">
+      <c r="E152" s="6"/>
+      <c r="F152" s="6" t="s">
+        <v>281</v>
+      </c>
+      <c r="G152" s="6">
         <v>75</v>
       </c>
     </row>
     <row r="153" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B153" t="s">
+      <c r="B153" s="6" t="s">
         <v>170</v>
       </c>
-      <c r="C153" t="s">
+      <c r="C153" s="6" t="s">
         <v>173</v>
       </c>
-      <c r="D153" t="s">
+      <c r="D153" s="6" t="s">
         <v>174</v>
       </c>
-      <c r="F153" t="s">
-        <v>281</v>
-      </c>
-      <c r="G153">
+      <c r="E153" s="6"/>
+      <c r="F153" s="6" t="s">
+        <v>281</v>
+      </c>
+      <c r="G153" s="6">
         <v>75</v>
       </c>
     </row>
     <row r="154" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B154" t="s">
+      <c r="B154" s="6" t="s">
         <v>170</v>
       </c>
-      <c r="C154" t="s">
+      <c r="C154" s="6" t="s">
         <v>175</v>
       </c>
-      <c r="D154" t="s">
+      <c r="D154" s="6" t="s">
         <v>176</v>
       </c>
-      <c r="F154" t="s">
-        <v>281</v>
-      </c>
-      <c r="G154">
+      <c r="E154" s="6"/>
+      <c r="F154" s="6" t="s">
+        <v>281</v>
+      </c>
+      <c r="G154" s="6">
         <v>75</v>
       </c>
     </row>
     <row r="155" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B155" t="s">
+      <c r="B155" s="6" t="s">
         <v>170</v>
       </c>
-      <c r="C155" t="s">
+      <c r="C155" s="6" t="s">
         <v>177</v>
       </c>
-      <c r="D155" t="s">
+      <c r="D155" s="6" t="s">
         <v>178</v>
       </c>
-      <c r="F155" t="s">
-        <v>281</v>
-      </c>
-      <c r="G155">
+      <c r="E155" s="6"/>
+      <c r="F155" s="6" t="s">
+        <v>281</v>
+      </c>
+      <c r="G155" s="6">
         <v>75</v>
       </c>
     </row>
     <row r="156" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B156" t="s">
+      <c r="B156" s="6" t="s">
         <v>170</v>
       </c>
-      <c r="C156" t="s">
+      <c r="C156" s="6" t="s">
         <v>168</v>
       </c>
-      <c r="D156" t="s">
+      <c r="D156" s="6" t="s">
         <v>179</v>
       </c>
-      <c r="F156" t="s">
-        <v>281</v>
-      </c>
-      <c r="G156">
+      <c r="E156" s="6"/>
+      <c r="F156" s="6" t="s">
+        <v>281</v>
+      </c>
+      <c r="G156" s="6">
         <v>75</v>
       </c>
     </row>
     <row r="157" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B157" t="s">
+      <c r="B157" s="6" t="s">
         <v>170</v>
       </c>
-      <c r="C157" t="s">
+      <c r="C157" s="6" t="s">
         <v>180</v>
       </c>
-      <c r="D157" t="s">
+      <c r="D157" s="6" t="s">
         <v>181</v>
       </c>
-      <c r="F157" t="s">
-        <v>281</v>
-      </c>
-      <c r="G157">
+      <c r="E157" s="6"/>
+      <c r="F157" s="6" t="s">
+        <v>281</v>
+      </c>
+      <c r="G157" s="6">
         <v>75</v>
       </c>
     </row>
+    <row r="158" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B158" s="6"/>
+      <c r="C158" s="6"/>
+      <c r="D158" s="6"/>
+      <c r="E158" s="6"/>
+      <c r="F158" s="6"/>
+      <c r="G158" s="6"/>
+    </row>
     <row r="159" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B159" t="s">
+      <c r="B159" s="6" t="s">
         <v>182</v>
       </c>
-      <c r="C159" t="s">
+      <c r="C159" s="6" t="s">
         <v>183</v>
       </c>
-      <c r="D159" t="s">
+      <c r="D159" s="6" t="s">
         <v>184</v>
       </c>
-      <c r="F159" t="s">
-        <v>281</v>
-      </c>
-      <c r="G159">
+      <c r="E159" s="6"/>
+      <c r="F159" s="6" t="s">
+        <v>281</v>
+      </c>
+      <c r="G159" s="6">
         <v>85</v>
       </c>
     </row>
     <row r="160" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B160" t="s">
+      <c r="B160" s="6" t="s">
         <v>182</v>
       </c>
-      <c r="C160" t="s">
+      <c r="C160" s="6" t="s">
         <v>185</v>
       </c>
-      <c r="D160" t="s">
+      <c r="D160" s="6" t="s">
         <v>220</v>
       </c>
-      <c r="F160" t="s">
-        <v>281</v>
-      </c>
-      <c r="G160">
+      <c r="E160" s="6"/>
+      <c r="F160" s="6" t="s">
+        <v>281</v>
+      </c>
+      <c r="G160" s="6">
         <v>85</v>
       </c>
     </row>
     <row r="161" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B161" t="s">
+      <c r="B161" s="6" t="s">
         <v>182</v>
       </c>
-      <c r="C161" t="s">
+      <c r="C161" s="6" t="s">
         <v>186</v>
       </c>
-      <c r="D161" t="s">
+      <c r="D161" s="6" t="s">
         <v>187</v>
       </c>
-      <c r="F161" t="s">
-        <v>281</v>
-      </c>
-      <c r="G161">
+      <c r="E161" s="6"/>
+      <c r="F161" s="6" t="s">
+        <v>281</v>
+      </c>
+      <c r="G161" s="6">
         <v>85</v>
       </c>
     </row>
     <row r="162" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B162" t="s">
+      <c r="B162" s="6" t="s">
         <v>182</v>
       </c>
-      <c r="C162" t="s">
+      <c r="C162" s="6" t="s">
         <v>188</v>
       </c>
-      <c r="D162" t="s">
+      <c r="D162" s="6" t="s">
         <v>189</v>
       </c>
-      <c r="F162" t="s">
-        <v>281</v>
-      </c>
-      <c r="G162">
+      <c r="E162" s="6"/>
+      <c r="F162" s="6" t="s">
+        <v>281</v>
+      </c>
+      <c r="G162" s="6">
         <v>85</v>
       </c>
     </row>
     <row r="163" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B163" t="s">
+      <c r="B163" s="6" t="s">
         <v>182</v>
       </c>
-      <c r="C163" t="s">
+      <c r="C163" s="6" t="s">
         <v>190</v>
       </c>
-      <c r="D163" t="s">
+      <c r="D163" s="6" t="s">
         <v>191</v>
       </c>
-      <c r="F163" t="s">
-        <v>281</v>
-      </c>
-      <c r="G163">
+      <c r="E163" s="6"/>
+      <c r="F163" s="6" t="s">
+        <v>281</v>
+      </c>
+      <c r="G163" s="6">
         <v>85</v>
       </c>
     </row>
     <row r="165" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B165" t="s">
+      <c r="B165" s="6" t="s">
         <v>221</v>
       </c>
-      <c r="C165" t="s">
+      <c r="C165" s="6" t="s">
         <v>222</v>
       </c>
-      <c r="D165" t="s">
+      <c r="D165" s="6" t="s">
         <v>223</v>
       </c>
-      <c r="F165" t="s">
+      <c r="E165" s="6"/>
+      <c r="F165" s="6" t="s">
         <v>242</v>
       </c>
-      <c r="G165">
+      <c r="G165" s="6">
         <v>85</v>
       </c>
     </row>
     <row r="166" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B166" t="s">
+      <c r="B166" s="6" t="s">
         <v>221</v>
       </c>
-      <c r="C166" t="s">
+      <c r="C166" s="6" t="s">
         <v>222</v>
       </c>
-      <c r="D166" t="s">
+      <c r="D166" s="6" t="s">
         <v>223</v>
       </c>
-      <c r="F166" t="s">
+      <c r="E166" s="6"/>
+      <c r="F166" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="G166">
+      <c r="G166" s="6">
         <v>100</v>
       </c>
     </row>
     <row r="167" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B167" t="s">
+      <c r="B167" s="6" t="s">
         <v>221</v>
       </c>
-      <c r="C167" t="s">
+      <c r="C167" s="6" t="s">
         <v>224</v>
       </c>
-      <c r="D167" t="s">
+      <c r="D167" s="6" t="s">
         <v>225</v>
       </c>
-      <c r="F167" t="s">
+      <c r="E167" s="6"/>
+      <c r="F167" s="6" t="s">
         <v>242</v>
       </c>
-      <c r="G167">
+      <c r="G167" s="6">
         <v>85</v>
       </c>
     </row>
     <row r="168" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B168" t="s">
+      <c r="B168" s="6" t="s">
         <v>221</v>
       </c>
-      <c r="C168" t="s">
+      <c r="C168" s="6" t="s">
         <v>224</v>
       </c>
-      <c r="D168" t="s">
+      <c r="D168" s="6" t="s">
         <v>225</v>
       </c>
-      <c r="F168" t="s">
+      <c r="E168" s="6"/>
+      <c r="F168" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="G168">
+      <c r="G168" s="6">
         <v>100</v>
       </c>
     </row>
     <row r="169" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B169" t="s">
+      <c r="B169" s="6" t="s">
         <v>221</v>
       </c>
-      <c r="C169" t="s">
+      <c r="C169" s="6" t="s">
         <v>226</v>
       </c>
-      <c r="D169" t="s">
+      <c r="D169" s="6" t="s">
         <v>227</v>
       </c>
-      <c r="F169" t="s">
+      <c r="E169" s="6"/>
+      <c r="F169" s="6" t="s">
         <v>242</v>
       </c>
-      <c r="G169">
+      <c r="G169" s="6">
         <v>85</v>
       </c>
     </row>
     <row r="170" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B170" t="s">
+      <c r="B170" s="6" t="s">
         <v>221</v>
       </c>
-      <c r="C170" t="s">
+      <c r="C170" s="6" t="s">
         <v>226</v>
       </c>
-      <c r="D170" t="s">
+      <c r="D170" s="6" t="s">
         <v>227</v>
       </c>
-      <c r="F170" t="s">
+      <c r="E170" s="6"/>
+      <c r="F170" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="G170">
+      <c r="G170" s="6">
         <v>100</v>
       </c>
     </row>
     <row r="171" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B171" t="s">
+      <c r="B171" s="6" t="s">
         <v>221</v>
       </c>
-      <c r="C171" t="s">
+      <c r="C171" s="6" t="s">
         <v>228</v>
       </c>
-      <c r="D171" t="s">
+      <c r="D171" s="6" t="s">
         <v>229</v>
       </c>
-      <c r="F171" t="s">
+      <c r="E171" s="6"/>
+      <c r="F171" s="6" t="s">
         <v>242</v>
       </c>
-      <c r="G171">
+      <c r="G171" s="6">
         <v>85</v>
       </c>
     </row>
     <row r="172" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B172" t="s">
+      <c r="B172" s="6" t="s">
         <v>221</v>
       </c>
-      <c r="C172" t="s">
+      <c r="C172" s="6" t="s">
         <v>228</v>
       </c>
-      <c r="D172" t="s">
+      <c r="D172" s="6" t="s">
         <v>229</v>
       </c>
-      <c r="F172" t="s">
+      <c r="E172" s="6"/>
+      <c r="F172" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="G172">
+      <c r="G172" s="6">
         <v>100</v>
       </c>
     </row>
     <row r="173" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B173" t="s">
+      <c r="B173" s="6" t="s">
         <v>221</v>
       </c>
-      <c r="C173" t="s">
+      <c r="C173" s="6" t="s">
         <v>230</v>
       </c>
-      <c r="D173" t="s">
+      <c r="D173" s="6" t="s">
         <v>231</v>
       </c>
-      <c r="F173" t="s">
+      <c r="E173" s="6"/>
+      <c r="F173" s="6" t="s">
         <v>242</v>
       </c>
-      <c r="G173">
+      <c r="G173" s="6">
         <v>85</v>
       </c>
     </row>
     <row r="174" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B174" t="s">
+      <c r="B174" s="6" t="s">
         <v>221</v>
       </c>
-      <c r="C174" t="s">
+      <c r="C174" s="6" t="s">
         <v>230</v>
       </c>
-      <c r="D174" t="s">
+      <c r="D174" s="6" t="s">
         <v>231</v>
       </c>
-      <c r="F174" t="s">
+      <c r="E174" s="6"/>
+      <c r="F174" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="G174">
+      <c r="G174" s="6">
         <v>100</v>
       </c>
     </row>
     <row r="175" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B175" t="s">
+      <c r="B175" s="6" t="s">
         <v>221</v>
       </c>
-      <c r="C175" t="s">
+      <c r="C175" s="6" t="s">
         <v>232</v>
       </c>
-      <c r="D175" t="s">
+      <c r="D175" s="6" t="s">
         <v>233</v>
       </c>
-      <c r="F175" t="s">
+      <c r="E175" s="6"/>
+      <c r="F175" s="6" t="s">
         <v>242</v>
       </c>
-      <c r="G175">
+      <c r="G175" s="6">
         <v>85</v>
       </c>
     </row>
     <row r="176" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B176" t="s">
+      <c r="B176" s="6" t="s">
         <v>221</v>
       </c>
-      <c r="C176" t="s">
+      <c r="C176" s="6" t="s">
         <v>232</v>
       </c>
-      <c r="D176" t="s">
+      <c r="D176" s="6" t="s">
         <v>233</v>
       </c>
-      <c r="F176" t="s">
+      <c r="E176" s="6"/>
+      <c r="F176" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="G176">
+      <c r="G176" s="6">
         <v>100</v>
       </c>
     </row>
     <row r="177" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B177" t="s">
+      <c r="B177" s="6" t="s">
         <v>221</v>
       </c>
-      <c r="C177" t="s">
+      <c r="C177" s="6" t="s">
         <v>234</v>
       </c>
-      <c r="D177" t="s">
+      <c r="D177" s="6" t="s">
         <v>235</v>
       </c>
-      <c r="F177" t="s">
+      <c r="E177" s="6"/>
+      <c r="F177" s="6" t="s">
         <v>242</v>
       </c>
-      <c r="G177">
+      <c r="G177" s="6">
         <v>85</v>
       </c>
     </row>
     <row r="178" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B178" t="s">
+      <c r="B178" s="6" t="s">
         <v>221</v>
       </c>
-      <c r="C178" t="s">
+      <c r="C178" s="6" t="s">
         <v>234</v>
       </c>
-      <c r="D178" t="s">
+      <c r="D178" s="6" t="s">
         <v>235</v>
       </c>
-      <c r="F178" t="s">
+      <c r="E178" s="6"/>
+      <c r="F178" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="G178">
+      <c r="G178" s="6">
         <v>100</v>
       </c>
     </row>
     <row r="179" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B179" t="s">
+      <c r="B179" s="6" t="s">
         <v>221</v>
       </c>
-      <c r="C179" t="s">
+      <c r="C179" s="6" t="s">
         <v>236</v>
       </c>
-      <c r="D179" t="s">
+      <c r="D179" s="6" t="s">
         <v>237</v>
       </c>
-      <c r="F179" t="s">
+      <c r="E179" s="6"/>
+      <c r="F179" s="6" t="s">
         <v>242</v>
       </c>
-      <c r="G179">
+      <c r="G179" s="6">
         <v>85</v>
       </c>
     </row>
     <row r="180" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B180" t="s">
+      <c r="B180" s="6" t="s">
         <v>221</v>
       </c>
-      <c r="C180" t="s">
+      <c r="C180" s="6" t="s">
         <v>236</v>
       </c>
-      <c r="D180" t="s">
+      <c r="D180" s="6" t="s">
         <v>237</v>
       </c>
-      <c r="F180" t="s">
+      <c r="E180" s="6"/>
+      <c r="F180" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="G180">
+      <c r="G180" s="6">
         <v>100</v>
       </c>
     </row>
     <row r="182" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B182" t="s">
+      <c r="B182" s="6" t="s">
         <v>240</v>
       </c>
-      <c r="C182" t="s">
+      <c r="C182" s="6" t="s">
         <v>247</v>
       </c>
-      <c r="D182" t="s">
+      <c r="D182" s="6" t="s">
         <v>241</v>
       </c>
-      <c r="F182" t="s">
+      <c r="E182" s="6"/>
+      <c r="F182" s="6" t="s">
         <v>242</v>
       </c>
-      <c r="G182">
+      <c r="G182" s="6">
         <v>90</v>
       </c>
     </row>
     <row r="183" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B183" t="s">
+      <c r="B183" s="6" t="s">
         <v>240</v>
       </c>
-      <c r="C183" t="s">
+      <c r="C183" s="6" t="s">
         <v>247</v>
       </c>
-      <c r="D183" t="s">
+      <c r="D183" s="6" t="s">
         <v>241</v>
       </c>
-      <c r="F183" t="s">
+      <c r="E183" s="6"/>
+      <c r="F183" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="G183">
+      <c r="G183" s="6">
         <v>110</v>
       </c>
     </row>
     <row r="184" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B184" t="s">
+      <c r="B184" s="6" t="s">
         <v>240</v>
       </c>
-      <c r="C184" t="s">
+      <c r="C184" s="6" t="s">
         <v>243</v>
       </c>
-      <c r="D184" t="s">
+      <c r="D184" s="6" t="s">
         <v>244</v>
       </c>
-      <c r="F184" t="s">
+      <c r="E184" s="6"/>
+      <c r="F184" s="6" t="s">
         <v>242</v>
       </c>
-      <c r="G184">
+      <c r="G184" s="6">
         <v>90</v>
       </c>
     </row>
     <row r="185" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B185" t="s">
+      <c r="B185" s="6" t="s">
         <v>240</v>
       </c>
-      <c r="C185" t="s">
+      <c r="C185" s="6" t="s">
         <v>243</v>
       </c>
-      <c r="D185" t="s">
+      <c r="D185" s="6" t="s">
         <v>244</v>
       </c>
-      <c r="F185" t="s">
+      <c r="E185" s="6"/>
+      <c r="F185" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="G185">
+      <c r="G185" s="6">
         <v>110</v>
       </c>
     </row>
     <row r="188" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B188" t="s">
+      <c r="B188" s="6" t="s">
         <v>245</v>
       </c>
-      <c r="C188" t="s">
+      <c r="C188" s="6" t="s">
         <v>246</v>
       </c>
-      <c r="D188" t="s">
+      <c r="D188" s="6" t="s">
         <v>249</v>
       </c>
-      <c r="E188" t="s">
+      <c r="E188" s="6" t="s">
         <v>248</v>
       </c>
-      <c r="F188" t="s">
+      <c r="F188" s="6" t="s">
         <v>242</v>
       </c>
-      <c r="G188">
+      <c r="G188" s="6">
         <v>90</v>
       </c>
-      <c r="J188" t="s">
+      <c r="H188" s="6"/>
+      <c r="I188" s="6"/>
+      <c r="J188" s="6" t="s">
         <v>327</v>
       </c>
-      <c r="K188" t="s">
+      <c r="K188" s="6" t="s">
         <v>251</v>
       </c>
     </row>
     <row r="189" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B189" t="s">
+      <c r="B189" s="6" t="s">
         <v>245</v>
       </c>
-      <c r="C189" t="s">
+      <c r="C189" s="6" t="s">
         <v>246</v>
       </c>
-      <c r="D189" t="s">
+      <c r="D189" s="6" t="s">
         <v>250</v>
       </c>
-      <c r="E189" t="s">
+      <c r="E189" s="6" t="s">
         <v>248</v>
       </c>
-      <c r="F189" t="s">
+      <c r="F189" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="G189">
+      <c r="G189" s="6">
         <v>110</v>
       </c>
-      <c r="J189" t="s">
+      <c r="H189" s="6"/>
+      <c r="I189" s="6"/>
+      <c r="J189" s="6" t="s">
         <v>327</v>
       </c>
-      <c r="K189" t="s">
+      <c r="K189" s="6" t="s">
         <v>251</v>
       </c>
     </row>
     <row r="192" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B192" t="s">
+      <c r="B192" s="6" t="s">
         <v>238</v>
       </c>
-      <c r="C192" t="s">
+      <c r="C192" s="6" t="s">
         <v>239</v>
       </c>
-      <c r="D192" t="s">
+      <c r="D192" s="6" t="s">
         <v>252</v>
       </c>
-      <c r="F192" t="s">
+      <c r="E192" s="6"/>
+      <c r="F192" s="6" t="s">
         <v>316</v>
       </c>
-      <c r="G192">
+      <c r="G192" s="6">
         <v>90</v>
       </c>
-      <c r="J192" t="s">
+      <c r="H192" s="6"/>
+      <c r="I192" s="6"/>
+      <c r="J192" s="6" t="s">
         <v>327</v>
       </c>
-      <c r="K192" t="s">
+      <c r="K192" s="6" t="s">
         <v>251</v>
       </c>
     </row>
     <row r="193" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B193" t="s">
+      <c r="B193" s="6" t="s">
         <v>238</v>
       </c>
-      <c r="C193" t="s">
+      <c r="C193" s="6" t="s">
         <v>253</v>
       </c>
-      <c r="D193" t="s">
+      <c r="D193" s="6" t="s">
         <v>254</v>
       </c>
-      <c r="F193" t="s">
+      <c r="E193" s="6"/>
+      <c r="F193" s="6" t="s">
         <v>316</v>
       </c>
-      <c r="G193">
+      <c r="G193" s="6">
         <v>110</v>
       </c>
-      <c r="J193" t="s">
+      <c r="H193" s="6"/>
+      <c r="I193" s="6"/>
+      <c r="J193" s="6" t="s">
         <v>327</v>
       </c>
-      <c r="K193" t="s">
+      <c r="K193" s="6" t="s">
         <v>251</v>
       </c>
     </row>
     <row r="194" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B194" t="s">
+      <c r="B194" s="6" t="s">
         <v>238</v>
       </c>
-      <c r="C194" t="s">
+      <c r="C194" s="6" t="s">
         <v>255</v>
       </c>
-      <c r="D194" t="s">
+      <c r="D194" s="6" t="s">
         <v>256</v>
       </c>
-      <c r="F194" t="s">
+      <c r="E194" s="6"/>
+      <c r="F194" s="6" t="s">
         <v>316</v>
       </c>
-      <c r="G194">
+      <c r="G194" s="6">
         <v>110</v>
       </c>
-      <c r="J194" t="s">
+      <c r="H194" s="6"/>
+      <c r="I194" s="6"/>
+      <c r="J194" s="6" t="s">
         <v>327</v>
       </c>
-      <c r="K194" t="s">
+      <c r="K194" s="6" t="s">
         <v>251</v>
       </c>
     </row>
     <row r="195" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B195" t="s">
+      <c r="B195" s="6" t="s">
         <v>238</v>
       </c>
-      <c r="C195" t="s">
+      <c r="C195" s="6" t="s">
         <v>257</v>
       </c>
-      <c r="D195" t="s">
+      <c r="D195" s="6" t="s">
         <v>258</v>
       </c>
-      <c r="F195" t="s">
+      <c r="E195" s="6"/>
+      <c r="F195" s="6" t="s">
         <v>316</v>
       </c>
-      <c r="G195">
+      <c r="G195" s="6">
         <v>80</v>
       </c>
-      <c r="J195" t="s">
+      <c r="H195" s="6"/>
+      <c r="I195" s="6"/>
+      <c r="J195" s="6" t="s">
         <v>327</v>
       </c>
-      <c r="K195" t="s">
+      <c r="K195" s="6" t="s">
         <v>251</v>
       </c>
     </row>
     <row r="196" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B196" t="s">
+      <c r="B196" s="6" t="s">
         <v>238</v>
       </c>
-      <c r="C196" t="s">
+      <c r="C196" s="6" t="s">
         <v>259</v>
       </c>
-      <c r="D196" t="s">
+      <c r="D196" s="6" t="s">
         <v>260</v>
       </c>
-      <c r="F196" t="s">
+      <c r="E196" s="6"/>
+      <c r="F196" s="6" t="s">
         <v>316</v>
       </c>
-      <c r="G196">
+      <c r="G196" s="6">
         <v>100</v>
       </c>
-      <c r="J196" t="s">
+      <c r="H196" s="6"/>
+      <c r="I196" s="6"/>
+      <c r="J196" s="6" t="s">
         <v>327</v>
       </c>
-      <c r="K196" t="s">
+      <c r="K196" s="6" t="s">
         <v>251</v>
       </c>
     </row>
     <row r="197" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B197" t="s">
+      <c r="B197" s="6" t="s">
         <v>238</v>
       </c>
-      <c r="C197" t="s">
+      <c r="C197" s="6" t="s">
         <v>261</v>
       </c>
-      <c r="D197" t="s">
+      <c r="D197" s="6" t="s">
         <v>262</v>
       </c>
-      <c r="E197" t="s">
+      <c r="E197" s="6" t="s">
         <v>263</v>
       </c>
-      <c r="F197" t="s">
+      <c r="F197" s="6" t="s">
         <v>316</v>
       </c>
-      <c r="G197">
+      <c r="G197" s="6">
         <v>90</v>
       </c>
-      <c r="J197" t="s">
+      <c r="H197" s="6"/>
+      <c r="I197" s="6"/>
+      <c r="J197" s="6" t="s">
         <v>327</v>
       </c>
-      <c r="K197" t="s">
+      <c r="K197" s="6" t="s">
         <v>251</v>
       </c>
     </row>
     <row r="200" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B200" t="s">
+      <c r="B200" s="6" t="s">
         <v>264</v>
       </c>
-      <c r="C200" t="s">
+      <c r="C200" s="6" t="s">
         <v>265</v>
       </c>
-      <c r="F200" t="s">
+      <c r="D200" s="6"/>
+      <c r="E200" s="6"/>
+      <c r="F200" s="6" t="s">
         <v>316</v>
       </c>
-      <c r="G200">
+      <c r="G200" s="6">
         <v>18</v>
       </c>
     </row>
     <row r="201" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B201" t="s">
+      <c r="B201" s="6" t="s">
         <v>264</v>
       </c>
-      <c r="C201" t="s">
+      <c r="C201" s="6" t="s">
         <v>266</v>
       </c>
-      <c r="F201" t="s">
+      <c r="D201" s="6"/>
+      <c r="E201" s="6"/>
+      <c r="F201" s="6" t="s">
         <v>316</v>
       </c>
-      <c r="G201">
+      <c r="G201" s="6">
         <v>20</v>
       </c>
     </row>
     <row r="202" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B202" t="s">
+      <c r="B202" s="6" t="s">
         <v>264</v>
       </c>
-      <c r="C202" t="s">
+      <c r="C202" s="6" t="s">
         <v>267</v>
       </c>
-      <c r="F202" t="s">
+      <c r="D202" s="6"/>
+      <c r="E202" s="6"/>
+      <c r="F202" s="6" t="s">
         <v>316</v>
       </c>
-      <c r="G202">
+      <c r="G202" s="6">
         <v>20</v>
       </c>
     </row>
     <row r="203" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B203" t="s">
+      <c r="B203" s="6" t="s">
         <v>264</v>
       </c>
-      <c r="C203" t="s">
+      <c r="C203" s="6" t="s">
         <v>268</v>
       </c>
-      <c r="F203" t="s">
+      <c r="D203" s="6"/>
+      <c r="E203" s="6"/>
+      <c r="F203" s="6" t="s">
         <v>316</v>
       </c>
-      <c r="G203">
+      <c r="G203" s="6">
         <v>28</v>
       </c>
     </row>
     <row r="204" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="C204" t="s">
+      <c r="B204" s="6"/>
+      <c r="C204" s="6" t="s">
         <v>251</v>
       </c>
-      <c r="F204" t="s">
+      <c r="D204" s="6"/>
+      <c r="E204" s="6"/>
+      <c r="F204" s="6" t="s">
         <v>315</v>
       </c>
-      <c r="G204">
+      <c r="G204" s="6">
         <v>20</v>
       </c>
     </row>
     <row r="206" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B206" t="s">
+      <c r="B206" s="6" t="s">
         <v>269</v>
       </c>
-      <c r="C206" t="s">
+      <c r="C206" s="6" t="s">
         <v>270</v>
       </c>
-      <c r="D206" t="s">
+      <c r="D206" s="6" t="s">
         <v>271</v>
       </c>
-      <c r="E206" t="s">
+      <c r="E206" s="6" t="s">
         <v>272</v>
       </c>
-      <c r="F206" t="s">
+      <c r="F206" s="6" t="s">
         <v>316</v>
       </c>
-      <c r="G206">
+      <c r="G206" s="6">
         <v>75</v>
       </c>
     </row>
@@ -4109,6 +4697,123 @@
       </c>
       <c r="G210">
         <v>95</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="C2:G16"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="2" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C2" t="s">
+        <v>192</v>
+      </c>
+      <c r="D2" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="3" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C3" t="s">
+        <v>201</v>
+      </c>
+      <c r="G3">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="4" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C4" t="s">
+        <v>193</v>
+      </c>
+      <c r="D4" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="5" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C5" t="s">
+        <v>195</v>
+      </c>
+      <c r="D5" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="6" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C6" t="s">
+        <v>197</v>
+      </c>
+      <c r="D6" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="7" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C7" t="s">
+        <v>199</v>
+      </c>
+      <c r="G7">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="9" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C9" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="10" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C10" t="s">
+        <v>203</v>
+      </c>
+      <c r="G10">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="11" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C11" t="s">
+        <v>204</v>
+      </c>
+      <c r="D11" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="12" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C12" t="s">
+        <v>195</v>
+      </c>
+      <c r="D12" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="13" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C13" t="s">
+        <v>197</v>
+      </c>
+      <c r="D13" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="14" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C14" t="s">
+        <v>208</v>
+      </c>
+      <c r="G14">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="16" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C16" t="s">
+        <v>169</v>
+      </c>
+      <c r="E16" t="s">
+        <v>284</v>
+      </c>
+      <c r="F16" t="s">
+        <v>315</v>
+      </c>
+      <c r="G16">
+        <v>15</v>
       </c>
     </row>
   </sheetData>
@@ -4118,117 +4823,4266 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="C2:G16"/>
+  <dimension ref="B2:J26"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="22" customWidth="1"/>
+    <col min="3" max="3" width="23.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="54.85546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="32" customWidth="1"/>
+    <col min="7" max="7" width="13.140625" customWidth="1"/>
+    <col min="8" max="10" width="18.7109375" customWidth="1"/>
+    <col min="11" max="11" width="24.42578125" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="2" spans="3:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B2" t="s">
+        <v>319</v>
+      </c>
       <c r="C2" t="s">
-        <v>192</v>
+        <v>320</v>
       </c>
       <c r="D2" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="3" spans="3:7" x14ac:dyDescent="0.25">
+        <v>321</v>
+      </c>
+      <c r="F2" t="s">
+        <v>336</v>
+      </c>
+      <c r="G2" t="s">
+        <v>324</v>
+      </c>
+      <c r="H2" t="s">
+        <v>325</v>
+      </c>
+      <c r="I2" t="s">
+        <v>337</v>
+      </c>
+      <c r="J2" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="3" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B3" t="s">
+        <v>30</v>
+      </c>
       <c r="C3" t="s">
-        <v>201</v>
+        <v>31</v>
+      </c>
+      <c r="D3" t="s">
+        <v>32</v>
+      </c>
+      <c r="F3" t="s">
+        <v>298</v>
       </c>
       <c r="G3">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="4" spans="3:7" x14ac:dyDescent="0.25">
+        <v>440</v>
+      </c>
+      <c r="H3" t="s">
+        <v>334</v>
+      </c>
+      <c r="I3" t="s">
+        <v>338</v>
+      </c>
+      <c r="J3" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="4" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B4" t="s">
+        <v>30</v>
+      </c>
       <c r="C4" t="s">
-        <v>193</v>
+        <v>33</v>
       </c>
       <c r="D4" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="5" spans="3:7" x14ac:dyDescent="0.25">
+        <v>34</v>
+      </c>
+      <c r="F4" t="s">
+        <v>308</v>
+      </c>
+      <c r="G4">
+        <v>310</v>
+      </c>
+      <c r="H4" t="s">
+        <v>334</v>
+      </c>
+      <c r="I4" t="s">
+        <v>338</v>
+      </c>
+      <c r="J4" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="5" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B5" t="s">
+        <v>30</v>
+      </c>
       <c r="C5" t="s">
-        <v>195</v>
+        <v>35</v>
       </c>
       <c r="D5" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="6" spans="3:7" x14ac:dyDescent="0.25">
+        <v>35</v>
+      </c>
+      <c r="F5" t="s">
+        <v>309</v>
+      </c>
+      <c r="G5">
+        <v>255</v>
+      </c>
+      <c r="H5" t="s">
+        <v>334</v>
+      </c>
+      <c r="I5" t="s">
+        <v>338</v>
+      </c>
+      <c r="J5" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="6" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B6" t="s">
+        <v>30</v>
+      </c>
       <c r="C6" t="s">
-        <v>197</v>
+        <v>36</v>
       </c>
       <c r="D6" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="7" spans="3:7" x14ac:dyDescent="0.25">
+        <v>37</v>
+      </c>
+      <c r="F6" t="s">
+        <v>304</v>
+      </c>
+      <c r="G6">
+        <v>280</v>
+      </c>
+      <c r="H6" t="s">
+        <v>334</v>
+      </c>
+      <c r="I6" t="s">
+        <v>338</v>
+      </c>
+      <c r="J6" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="7" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B7" t="s">
+        <v>30</v>
+      </c>
       <c r="C7" t="s">
-        <v>199</v>
+        <v>38</v>
+      </c>
+      <c r="D7" t="s">
+        <v>41</v>
+      </c>
+      <c r="F7" t="s">
+        <v>305</v>
       </c>
       <c r="G7">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="9" spans="3:7" x14ac:dyDescent="0.25">
+        <v>210</v>
+      </c>
+      <c r="H7" t="s">
+        <v>334</v>
+      </c>
+      <c r="I7" t="s">
+        <v>338</v>
+      </c>
+      <c r="J7" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="8" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B8" t="s">
+        <v>30</v>
+      </c>
+      <c r="C8" t="s">
+        <v>39</v>
+      </c>
+      <c r="D8" t="s">
+        <v>40</v>
+      </c>
+      <c r="F8" t="s">
+        <v>302</v>
+      </c>
+      <c r="G8">
+        <v>190</v>
+      </c>
+      <c r="H8" t="s">
+        <v>334</v>
+      </c>
+      <c r="I8" t="s">
+        <v>338</v>
+      </c>
+      <c r="J8" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="9" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B9" t="s">
+        <v>30</v>
+      </c>
       <c r="C9" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="10" spans="3:7" x14ac:dyDescent="0.25">
+        <v>42</v>
+      </c>
+      <c r="D9" t="s">
+        <v>43</v>
+      </c>
+      <c r="F9" t="s">
+        <v>303</v>
+      </c>
+      <c r="G9">
+        <v>170</v>
+      </c>
+      <c r="H9" t="s">
+        <v>334</v>
+      </c>
+      <c r="I9" t="s">
+        <v>338</v>
+      </c>
+      <c r="J9" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="10" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B10" t="s">
+        <v>30</v>
+      </c>
       <c r="C10" t="s">
-        <v>203</v>
-      </c>
-      <c r="G10">
+        <v>44</v>
+      </c>
+      <c r="D10" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="11" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B11" t="s">
+        <v>30</v>
+      </c>
+      <c r="C11" t="s">
+        <v>46</v>
+      </c>
+      <c r="D11" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="12" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B12" t="s">
+        <v>30</v>
+      </c>
+      <c r="C12" t="s">
+        <v>48</v>
+      </c>
+      <c r="D12" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="13" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B13" t="s">
+        <v>30</v>
+      </c>
+      <c r="C13" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="11" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C11" t="s">
-        <v>204</v>
-      </c>
-      <c r="D11" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="12" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C12" t="s">
-        <v>195</v>
-      </c>
-      <c r="D12" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="13" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C13" t="s">
-        <v>197</v>
-      </c>
       <c r="D13" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="14" spans="3:7" x14ac:dyDescent="0.25">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="14" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B14" t="s">
+        <v>30</v>
+      </c>
       <c r="C14" t="s">
-        <v>208</v>
-      </c>
-      <c r="G14">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="16" spans="3:7" x14ac:dyDescent="0.25">
+        <v>52</v>
+      </c>
+      <c r="D14" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="15" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B15" t="s">
+        <v>30</v>
+      </c>
+      <c r="C15" t="s">
+        <v>54</v>
+      </c>
+      <c r="D15" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="16" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B16" t="s">
+        <v>30</v>
+      </c>
       <c r="C16" t="s">
-        <v>169</v>
-      </c>
-      <c r="E16" t="s">
-        <v>284</v>
-      </c>
-      <c r="F16" t="s">
-        <v>315</v>
-      </c>
-      <c r="G16">
-        <v>15</v>
+        <v>56</v>
+      </c>
+      <c r="D16" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="20" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B20" t="s">
+        <v>319</v>
+      </c>
+      <c r="C20" t="s">
+        <v>320</v>
+      </c>
+      <c r="D20" t="s">
+        <v>321</v>
+      </c>
+      <c r="F20" t="s">
+        <v>335</v>
+      </c>
+      <c r="G20" t="s">
+        <v>324</v>
+      </c>
+      <c r="H20" t="s">
+        <v>325</v>
+      </c>
+      <c r="I20" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="21" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B21" t="s">
+        <v>59</v>
+      </c>
+      <c r="C21" t="s">
+        <v>60</v>
+      </c>
+      <c r="D21" t="s">
+        <v>297</v>
+      </c>
+      <c r="F21" t="s">
+        <v>24</v>
+      </c>
+      <c r="G21">
+        <v>470</v>
+      </c>
+      <c r="H21" t="s">
+        <v>334</v>
+      </c>
+      <c r="I21" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="22" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="F22" t="s">
+        <v>308</v>
+      </c>
+      <c r="G22">
+        <v>340</v>
+      </c>
+      <c r="H22" t="s">
+        <v>334</v>
+      </c>
+      <c r="I22" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="23" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="F23" t="s">
+        <v>309</v>
+      </c>
+      <c r="G23">
+        <v>285</v>
+      </c>
+      <c r="H23" t="s">
+        <v>334</v>
+      </c>
+      <c r="I23" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="24" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="F24" t="s">
+        <v>26</v>
+      </c>
+      <c r="G24">
+        <v>310</v>
+      </c>
+      <c r="H24" t="s">
+        <v>334</v>
+      </c>
+      <c r="I24" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="25" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="F25" t="s">
+        <v>29</v>
+      </c>
+      <c r="G25">
+        <v>245</v>
+      </c>
+      <c r="H25" t="s">
+        <v>334</v>
+      </c>
+      <c r="I25" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="26" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="F26" t="s">
+        <v>27</v>
+      </c>
+      <c r="G26">
+        <v>215</v>
+      </c>
+      <c r="H26" t="s">
+        <v>334</v>
+      </c>
+      <c r="I26" t="s">
+        <v>338</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="4">
+    <tablePart r:id="rId1"/>
+    <tablePart r:id="rId2"/>
+    <tablePart r:id="rId3"/>
+    <tablePart r:id="rId4"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="B2:J14"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="18.140625" customWidth="1"/>
+    <col min="3" max="3" width="25.7109375" customWidth="1"/>
+    <col min="4" max="4" width="77.5703125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="20.42578125" customWidth="1"/>
+    <col min="9" max="9" width="14.7109375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="21.42578125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B2" t="s">
+        <v>319</v>
+      </c>
+      <c r="C2" t="s">
+        <v>320</v>
+      </c>
+      <c r="D2" t="s">
+        <v>321</v>
+      </c>
+      <c r="E2" t="s">
+        <v>323</v>
+      </c>
+      <c r="F2" t="s">
+        <v>324</v>
+      </c>
+      <c r="G2" t="s">
+        <v>325</v>
+      </c>
+      <c r="H2" t="s">
+        <v>337</v>
+      </c>
+      <c r="I2" t="s">
+        <v>359</v>
+      </c>
+      <c r="J2" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="3" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B3" t="s">
+        <v>66</v>
+      </c>
+      <c r="C3" t="s">
+        <v>67</v>
+      </c>
+      <c r="D3" t="s">
+        <v>365</v>
+      </c>
+      <c r="E3" t="s">
+        <v>318</v>
+      </c>
+      <c r="F3">
+        <v>65</v>
+      </c>
+      <c r="G3" t="s">
+        <v>310</v>
+      </c>
+      <c r="H3" t="s">
+        <v>92</v>
+      </c>
+      <c r="I3" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="4" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B4" t="s">
+        <v>66</v>
+      </c>
+      <c r="C4" t="s">
+        <v>69</v>
+      </c>
+      <c r="D4" t="s">
+        <v>366</v>
+      </c>
+      <c r="E4" t="s">
+        <v>318</v>
+      </c>
+      <c r="F4">
+        <v>65</v>
+      </c>
+      <c r="G4" t="s">
+        <v>310</v>
+      </c>
+      <c r="H4" t="s">
+        <v>92</v>
+      </c>
+      <c r="I4" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="5" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B5" t="s">
+        <v>66</v>
+      </c>
+      <c r="C5" t="s">
+        <v>71</v>
+      </c>
+      <c r="D5" t="s">
+        <v>364</v>
+      </c>
+      <c r="E5" t="s">
+        <v>318</v>
+      </c>
+      <c r="F5">
+        <v>100</v>
+      </c>
+      <c r="G5" t="s">
+        <v>310</v>
+      </c>
+      <c r="H5" t="s">
+        <v>92</v>
+      </c>
+      <c r="I5" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="6" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B6" t="s">
+        <v>66</v>
+      </c>
+      <c r="C6" t="s">
+        <v>73</v>
+      </c>
+      <c r="D6" t="s">
+        <v>363</v>
+      </c>
+      <c r="E6" t="s">
+        <v>318</v>
+      </c>
+      <c r="F6">
+        <v>110</v>
+      </c>
+      <c r="G6" t="s">
+        <v>310</v>
+      </c>
+      <c r="H6" t="s">
+        <v>92</v>
+      </c>
+      <c r="I6" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="7" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B7" t="s">
+        <v>66</v>
+      </c>
+      <c r="C7" t="s">
+        <v>75</v>
+      </c>
+      <c r="D7" t="s">
+        <v>362</v>
+      </c>
+      <c r="E7" t="s">
+        <v>318</v>
+      </c>
+      <c r="F7">
+        <v>110</v>
+      </c>
+      <c r="G7" t="s">
+        <v>310</v>
+      </c>
+      <c r="H7" t="s">
+        <v>92</v>
+      </c>
+      <c r="I7" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="8" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B8" t="s">
+        <v>66</v>
+      </c>
+      <c r="C8" t="s">
+        <v>77</v>
+      </c>
+      <c r="D8" t="s">
+        <v>367</v>
+      </c>
+      <c r="E8" t="s">
+        <v>318</v>
+      </c>
+      <c r="F8">
+        <v>265</v>
+      </c>
+      <c r="G8" t="s">
+        <v>310</v>
+      </c>
+      <c r="H8" t="s">
+        <v>92</v>
+      </c>
+      <c r="I8" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="9" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B9" t="s">
+        <v>66</v>
+      </c>
+      <c r="C9" t="s">
+        <v>79</v>
+      </c>
+      <c r="D9" t="s">
+        <v>368</v>
+      </c>
+      <c r="E9" t="s">
+        <v>318</v>
+      </c>
+      <c r="F9">
+        <v>390</v>
+      </c>
+      <c r="G9" t="s">
+        <v>310</v>
+      </c>
+      <c r="H9" t="s">
+        <v>92</v>
+      </c>
+      <c r="I9" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="10" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B10" t="s">
+        <v>66</v>
+      </c>
+      <c r="C10" t="s">
+        <v>81</v>
+      </c>
+      <c r="D10" t="s">
+        <v>369</v>
+      </c>
+      <c r="E10" t="s">
+        <v>318</v>
+      </c>
+      <c r="F10">
+        <v>310</v>
+      </c>
+      <c r="G10" t="s">
+        <v>310</v>
+      </c>
+      <c r="H10" t="s">
+        <v>92</v>
+      </c>
+      <c r="I10" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="11" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B11" t="s">
+        <v>66</v>
+      </c>
+      <c r="C11" t="s">
+        <v>83</v>
+      </c>
+      <c r="D11" t="s">
+        <v>370</v>
+      </c>
+      <c r="E11" t="s">
+        <v>318</v>
+      </c>
+      <c r="F11">
+        <v>360</v>
+      </c>
+      <c r="G11" t="s">
+        <v>310</v>
+      </c>
+      <c r="H11" t="s">
+        <v>92</v>
+      </c>
+      <c r="I11" t="s">
+        <v>358</v>
+      </c>
+      <c r="J11" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="12" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B12" t="s">
+        <v>66</v>
+      </c>
+      <c r="C12" t="s">
+        <v>85</v>
+      </c>
+      <c r="D12" t="s">
+        <v>371</v>
+      </c>
+      <c r="E12" t="s">
+        <v>318</v>
+      </c>
+      <c r="F12">
+        <v>610</v>
+      </c>
+      <c r="G12" t="s">
+        <v>310</v>
+      </c>
+      <c r="H12" t="s">
+        <v>92</v>
+      </c>
+      <c r="I12" t="s">
+        <v>358</v>
+      </c>
+      <c r="J12" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="13" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B13" t="s">
+        <v>87</v>
+      </c>
+      <c r="C13" t="s">
+        <v>90</v>
+      </c>
+      <c r="D13" t="s">
+        <v>372</v>
+      </c>
+      <c r="E13" t="s">
+        <v>317</v>
+      </c>
+      <c r="F13">
+        <v>400</v>
+      </c>
+      <c r="G13" s="3" t="s">
+        <v>310</v>
+      </c>
+      <c r="H13" t="s">
+        <v>92</v>
+      </c>
+      <c r="I13" t="s">
+        <v>358</v>
+      </c>
+      <c r="J13" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="14" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B14" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>373</v>
+      </c>
+      <c r="E14" s="4" t="s">
+        <v>317</v>
+      </c>
+      <c r="F14" s="4">
+        <v>360</v>
+      </c>
+      <c r="G14" s="5" t="s">
+        <v>310</v>
+      </c>
+      <c r="H14" t="s">
+        <v>92</v>
+      </c>
+      <c r="I14" t="s">
+        <v>358</v>
+      </c>
+      <c r="J14" t="s">
+        <v>361</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="B2:I25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="20.5703125" customWidth="1"/>
+    <col min="3" max="3" width="19.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="64.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="31.7109375" customWidth="1"/>
+    <col min="7" max="7" width="8.7109375" customWidth="1"/>
+    <col min="8" max="8" width="17.140625" customWidth="1"/>
+    <col min="9" max="9" width="27.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B2" t="s">
+        <v>319</v>
+      </c>
+      <c r="C2" t="s">
+        <v>320</v>
+      </c>
+      <c r="D2" t="s">
+        <v>321</v>
+      </c>
+      <c r="F2" t="s">
+        <v>332</v>
+      </c>
+      <c r="G2" t="s">
+        <v>324</v>
+      </c>
+      <c r="H2" t="s">
+        <v>325</v>
+      </c>
+      <c r="I2" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="3" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B3" t="s">
+        <v>296</v>
+      </c>
+      <c r="C3" t="s">
+        <v>0</v>
+      </c>
+      <c r="D3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F3" t="s">
+        <v>298</v>
+      </c>
+      <c r="G3">
+        <v>500</v>
+      </c>
+      <c r="H3" t="s">
+        <v>334</v>
+      </c>
+      <c r="I3" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="4" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B4" t="s">
+        <v>296</v>
+      </c>
+      <c r="C4" t="s">
+        <v>2</v>
+      </c>
+      <c r="D4" t="s">
+        <v>3</v>
+      </c>
+      <c r="F4" t="s">
+        <v>308</v>
+      </c>
+      <c r="G4">
+        <v>360</v>
+      </c>
+      <c r="H4" t="s">
+        <v>334</v>
+      </c>
+      <c r="I4" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="5" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B5" t="s">
+        <v>296</v>
+      </c>
+      <c r="C5" t="s">
+        <v>4</v>
+      </c>
+      <c r="D5" t="s">
+        <v>5</v>
+      </c>
+      <c r="F5" t="s">
+        <v>309</v>
+      </c>
+      <c r="G5">
+        <v>300</v>
+      </c>
+      <c r="H5" t="s">
+        <v>334</v>
+      </c>
+      <c r="I5" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="6" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B6" t="s">
+        <v>296</v>
+      </c>
+      <c r="C6" t="s">
+        <v>6</v>
+      </c>
+      <c r="D6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F6" t="s">
+        <v>304</v>
+      </c>
+      <c r="G6">
+        <v>300</v>
+      </c>
+      <c r="H6" t="s">
+        <v>334</v>
+      </c>
+      <c r="I6" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="7" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B7" t="s">
+        <v>296</v>
+      </c>
+      <c r="C7" t="s">
+        <v>8</v>
+      </c>
+      <c r="D7" t="s">
+        <v>9</v>
+      </c>
+      <c r="F7" t="s">
+        <v>305</v>
+      </c>
+      <c r="G7">
+        <v>280</v>
+      </c>
+      <c r="H7" t="s">
+        <v>334</v>
+      </c>
+      <c r="I7" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="8" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B8" t="s">
+        <v>296</v>
+      </c>
+      <c r="C8" t="s">
+        <v>10</v>
+      </c>
+      <c r="D8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F8" t="s">
+        <v>302</v>
+      </c>
+      <c r="G8">
+        <v>230</v>
+      </c>
+      <c r="H8" t="s">
+        <v>334</v>
+      </c>
+      <c r="I8" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="9" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B9" t="s">
+        <v>296</v>
+      </c>
+      <c r="C9" t="s">
+        <v>12</v>
+      </c>
+      <c r="D9" t="s">
+        <v>13</v>
+      </c>
+      <c r="F9" t="s">
+        <v>303</v>
+      </c>
+      <c r="G9">
+        <v>200</v>
+      </c>
+      <c r="H9" t="s">
+        <v>334</v>
+      </c>
+      <c r="I9" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="10" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B10" t="s">
+        <v>296</v>
+      </c>
+      <c r="C10" t="s">
+        <v>14</v>
+      </c>
+      <c r="D10" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="11" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B11" t="s">
+        <v>296</v>
+      </c>
+      <c r="C11" t="s">
+        <v>16</v>
+      </c>
+      <c r="D11" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="14" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B14" t="s">
+        <v>319</v>
+      </c>
+      <c r="C14" t="s">
+        <v>320</v>
+      </c>
+      <c r="D14" t="s">
+        <v>321</v>
+      </c>
+      <c r="F14" t="s">
+        <v>333</v>
+      </c>
+      <c r="G14" t="s">
+        <v>324</v>
+      </c>
+      <c r="H14" t="s">
+        <v>325</v>
+      </c>
+      <c r="I14" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="15" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B15" t="s">
+        <v>306</v>
+      </c>
+      <c r="C15" t="s">
+        <v>307</v>
+      </c>
+      <c r="D15" t="s">
+        <v>18</v>
+      </c>
+      <c r="F15" t="s">
+        <v>298</v>
+      </c>
+      <c r="G15">
+        <v>460</v>
+      </c>
+      <c r="H15" t="s">
+        <v>334</v>
+      </c>
+      <c r="I15" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="16" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B16" t="s">
+        <v>306</v>
+      </c>
+      <c r="C16" t="s">
+        <v>307</v>
+      </c>
+      <c r="D16" t="s">
+        <v>19</v>
+      </c>
+      <c r="F16" t="s">
+        <v>308</v>
+      </c>
+      <c r="G16">
+        <v>310</v>
+      </c>
+      <c r="H16" t="s">
+        <v>334</v>
+      </c>
+      <c r="I16" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="17" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B17" t="s">
+        <v>306</v>
+      </c>
+      <c r="C17" t="s">
+        <v>307</v>
+      </c>
+      <c r="D17" t="s">
+        <v>20</v>
+      </c>
+      <c r="F17" t="s">
+        <v>309</v>
+      </c>
+      <c r="G17">
+        <v>225</v>
+      </c>
+      <c r="H17" t="s">
+        <v>334</v>
+      </c>
+      <c r="I17" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="18" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="F18" t="s">
+        <v>301</v>
+      </c>
+      <c r="G18">
+        <v>195</v>
+      </c>
+      <c r="H18" t="s">
+        <v>334</v>
+      </c>
+      <c r="I18" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="19" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="F19" t="s">
+        <v>302</v>
+      </c>
+      <c r="G19">
+        <v>170</v>
+      </c>
+      <c r="H19" t="s">
+        <v>334</v>
+      </c>
+      <c r="I19" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="20" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="F20" t="s">
+        <v>303</v>
+      </c>
+      <c r="G20">
+        <v>140</v>
+      </c>
+      <c r="H20" t="s">
+        <v>334</v>
+      </c>
+      <c r="I20" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="23" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B23" t="s">
+        <v>319</v>
+      </c>
+      <c r="C23" t="s">
+        <v>320</v>
+      </c>
+      <c r="D23" t="s">
+        <v>321</v>
+      </c>
+      <c r="F23" t="s">
+        <v>323</v>
+      </c>
+      <c r="G23" t="s">
+        <v>324</v>
+      </c>
+      <c r="H23" t="s">
+        <v>325</v>
+      </c>
+      <c r="I23" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="24" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B24" t="s">
+        <v>330</v>
+      </c>
+      <c r="C24" t="s">
+        <v>22</v>
+      </c>
+      <c r="F24" t="s">
+        <v>331</v>
+      </c>
+      <c r="G24">
+        <v>110</v>
+      </c>
+      <c r="H24" t="s">
+        <v>334</v>
+      </c>
+      <c r="I24" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="25" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B25" t="s">
+        <v>330</v>
+      </c>
+      <c r="C25" t="s">
+        <v>23</v>
+      </c>
+      <c r="F25" t="s">
+        <v>331</v>
+      </c>
+      <c r="G25">
+        <v>110</v>
+      </c>
+      <c r="H25" t="s">
+        <v>334</v>
+      </c>
+      <c r="I25" t="s">
+        <v>338</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="0" orientation="portrait" horizontalDpi="203" verticalDpi="203" r:id="rId1"/>
+  <tableParts count="6">
+    <tablePart r:id="rId2"/>
+    <tablePart r:id="rId3"/>
+    <tablePart r:id="rId4"/>
+    <tablePart r:id="rId5"/>
+    <tablePart r:id="rId6"/>
+    <tablePart r:id="rId7"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="B2:J14"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="24.140625" customWidth="1"/>
+    <col min="3" max="3" width="29.5703125" customWidth="1"/>
+    <col min="4" max="4" width="53" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="28.42578125" customWidth="1"/>
+    <col min="7" max="7" width="8.7109375" customWidth="1"/>
+    <col min="8" max="8" width="17.42578125" customWidth="1"/>
+    <col min="9" max="9" width="20.5703125" customWidth="1"/>
+    <col min="10" max="10" width="15.140625" customWidth="1"/>
+    <col min="11" max="11" width="14.5703125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B2" t="s">
+        <v>319</v>
+      </c>
+      <c r="C2" t="s">
+        <v>320</v>
+      </c>
+      <c r="D2" t="s">
+        <v>321</v>
+      </c>
+      <c r="E2" t="s">
+        <v>322</v>
+      </c>
+      <c r="F2" t="s">
+        <v>323</v>
+      </c>
+      <c r="G2" t="s">
+        <v>324</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>337</v>
+      </c>
+      <c r="J2" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="3" spans="2:10" ht="45" x14ac:dyDescent="0.25">
+      <c r="B3" t="s">
+        <v>166</v>
+      </c>
+      <c r="C3" t="s">
+        <v>167</v>
+      </c>
+      <c r="E3" s="7" t="s">
+        <v>283</v>
+      </c>
+      <c r="F3" t="s">
+        <v>281</v>
+      </c>
+      <c r="G3">
+        <v>45</v>
+      </c>
+      <c r="H3" t="s">
+        <v>334</v>
+      </c>
+      <c r="I3" t="s">
+        <v>338</v>
+      </c>
+      <c r="J3" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="4" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B4" t="s">
+        <v>170</v>
+      </c>
+      <c r="C4" t="s">
+        <v>171</v>
+      </c>
+      <c r="D4" t="s">
+        <v>172</v>
+      </c>
+      <c r="F4" t="s">
+        <v>281</v>
+      </c>
+      <c r="G4">
+        <v>75</v>
+      </c>
+      <c r="H4" t="s">
+        <v>334</v>
+      </c>
+      <c r="I4" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="5" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B5" t="s">
+        <v>170</v>
+      </c>
+      <c r="C5" t="s">
+        <v>173</v>
+      </c>
+      <c r="D5" t="s">
+        <v>174</v>
+      </c>
+      <c r="F5" t="s">
+        <v>281</v>
+      </c>
+      <c r="G5">
+        <v>75</v>
+      </c>
+      <c r="H5" t="s">
+        <v>334</v>
+      </c>
+      <c r="I5" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="6" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B6" t="s">
+        <v>170</v>
+      </c>
+      <c r="C6" t="s">
+        <v>175</v>
+      </c>
+      <c r="D6" t="s">
+        <v>176</v>
+      </c>
+      <c r="F6" t="s">
+        <v>281</v>
+      </c>
+      <c r="G6">
+        <v>75</v>
+      </c>
+      <c r="H6" t="s">
+        <v>334</v>
+      </c>
+      <c r="I6" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="7" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B7" t="s">
+        <v>170</v>
+      </c>
+      <c r="C7" t="s">
+        <v>177</v>
+      </c>
+      <c r="D7" t="s">
+        <v>178</v>
+      </c>
+      <c r="F7" t="s">
+        <v>281</v>
+      </c>
+      <c r="G7">
+        <v>75</v>
+      </c>
+      <c r="H7" t="s">
+        <v>334</v>
+      </c>
+      <c r="I7" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="8" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B8" t="s">
+        <v>170</v>
+      </c>
+      <c r="C8" t="s">
+        <v>168</v>
+      </c>
+      <c r="D8" t="s">
+        <v>179</v>
+      </c>
+      <c r="F8" t="s">
+        <v>281</v>
+      </c>
+      <c r="G8">
+        <v>75</v>
+      </c>
+      <c r="H8" t="s">
+        <v>334</v>
+      </c>
+      <c r="I8" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="9" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B9" t="s">
+        <v>170</v>
+      </c>
+      <c r="C9" t="s">
+        <v>180</v>
+      </c>
+      <c r="D9" t="s">
+        <v>181</v>
+      </c>
+      <c r="F9" t="s">
+        <v>281</v>
+      </c>
+      <c r="G9">
+        <v>75</v>
+      </c>
+      <c r="H9" t="s">
+        <v>334</v>
+      </c>
+      <c r="I9" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="10" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B10" t="s">
+        <v>182</v>
+      </c>
+      <c r="C10" t="s">
+        <v>183</v>
+      </c>
+      <c r="D10" t="s">
+        <v>184</v>
+      </c>
+      <c r="F10" t="s">
+        <v>281</v>
+      </c>
+      <c r="G10">
+        <v>85</v>
+      </c>
+      <c r="H10" t="s">
+        <v>334</v>
+      </c>
+      <c r="I10" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="11" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B11" t="s">
+        <v>182</v>
+      </c>
+      <c r="C11" t="s">
+        <v>185</v>
+      </c>
+      <c r="D11" t="s">
+        <v>220</v>
+      </c>
+      <c r="F11" t="s">
+        <v>281</v>
+      </c>
+      <c r="G11">
+        <v>85</v>
+      </c>
+      <c r="H11" t="s">
+        <v>334</v>
+      </c>
+      <c r="I11" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="12" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B12" t="s">
+        <v>182</v>
+      </c>
+      <c r="C12" t="s">
+        <v>186</v>
+      </c>
+      <c r="D12" t="s">
+        <v>187</v>
+      </c>
+      <c r="F12" t="s">
+        <v>281</v>
+      </c>
+      <c r="G12">
+        <v>85</v>
+      </c>
+      <c r="H12" t="s">
+        <v>334</v>
+      </c>
+      <c r="I12" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="13" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B13" t="s">
+        <v>182</v>
+      </c>
+      <c r="C13" t="s">
+        <v>188</v>
+      </c>
+      <c r="D13" t="s">
+        <v>189</v>
+      </c>
+      <c r="F13" t="s">
+        <v>281</v>
+      </c>
+      <c r="G13">
+        <v>85</v>
+      </c>
+      <c r="H13" t="s">
+        <v>334</v>
+      </c>
+      <c r="I13" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="14" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B14" t="s">
+        <v>182</v>
+      </c>
+      <c r="C14" t="s">
+        <v>190</v>
+      </c>
+      <c r="D14" t="s">
+        <v>191</v>
+      </c>
+      <c r="F14" t="s">
+        <v>281</v>
+      </c>
+      <c r="G14">
+        <v>85</v>
+      </c>
+      <c r="H14" t="s">
+        <v>334</v>
+      </c>
+      <c r="I14" t="s">
+        <v>338</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="B2:J89"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="26.42578125" customWidth="1"/>
+    <col min="3" max="3" width="30.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="48.5703125" customWidth="1"/>
+    <col min="5" max="5" width="85.42578125" customWidth="1"/>
+    <col min="8" max="8" width="15.7109375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="18.5703125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="19.85546875" customWidth="1"/>
+    <col min="11" max="11" width="14.5703125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B2" t="s">
+        <v>319</v>
+      </c>
+      <c r="C2" t="s">
+        <v>320</v>
+      </c>
+      <c r="D2" t="s">
+        <v>321</v>
+      </c>
+      <c r="E2" t="s">
+        <v>322</v>
+      </c>
+      <c r="F2" t="s">
+        <v>323</v>
+      </c>
+      <c r="G2" t="s">
+        <v>324</v>
+      </c>
+      <c r="H2" t="s">
+        <v>325</v>
+      </c>
+      <c r="I2" t="s">
+        <v>337</v>
+      </c>
+      <c r="J2" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="3" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B3" t="s">
+        <v>61</v>
+      </c>
+      <c r="C3" t="s">
+        <v>62</v>
+      </c>
+      <c r="F3" t="s">
+        <v>281</v>
+      </c>
+      <c r="G3">
+        <v>120</v>
+      </c>
+      <c r="H3" t="s">
+        <v>334</v>
+      </c>
+      <c r="I3" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="4" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B4" t="s">
+        <v>61</v>
+      </c>
+      <c r="C4" t="s">
+        <v>63</v>
+      </c>
+      <c r="F4" t="s">
+        <v>281</v>
+      </c>
+      <c r="G4">
+        <v>35</v>
+      </c>
+      <c r="H4" t="s">
+        <v>334</v>
+      </c>
+      <c r="I4" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="5" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B5" t="s">
+        <v>61</v>
+      </c>
+      <c r="C5" t="s">
+        <v>356</v>
+      </c>
+      <c r="F5" t="s">
+        <v>281</v>
+      </c>
+      <c r="G5">
+        <v>100</v>
+      </c>
+      <c r="H5" t="s">
+        <v>334</v>
+      </c>
+      <c r="I5" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="6" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B6" t="s">
+        <v>61</v>
+      </c>
+      <c r="C6" t="s">
+        <v>65</v>
+      </c>
+      <c r="F6" t="s">
+        <v>281</v>
+      </c>
+      <c r="G6">
+        <v>100</v>
+      </c>
+      <c r="H6" t="s">
+        <v>334</v>
+      </c>
+      <c r="I6" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="7" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B7" t="s">
+        <v>289</v>
+      </c>
+      <c r="C7" t="s">
+        <v>288</v>
+      </c>
+      <c r="F7" t="s">
+        <v>281</v>
+      </c>
+      <c r="G7">
+        <v>50</v>
+      </c>
+      <c r="H7" t="s">
+        <v>334</v>
+      </c>
+      <c r="I7" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="8" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B8" t="s">
+        <v>289</v>
+      </c>
+      <c r="C8" t="s">
+        <v>287</v>
+      </c>
+      <c r="F8" t="s">
+        <v>281</v>
+      </c>
+      <c r="G8">
+        <v>75</v>
+      </c>
+      <c r="H8" t="s">
+        <v>334</v>
+      </c>
+      <c r="I8" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="9" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B9" t="s">
+        <v>289</v>
+      </c>
+      <c r="C9" t="s">
+        <v>286</v>
+      </c>
+      <c r="F9" t="s">
+        <v>281</v>
+      </c>
+      <c r="G9">
+        <v>75</v>
+      </c>
+      <c r="H9" t="s">
+        <v>334</v>
+      </c>
+      <c r="I9" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="10" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B10" t="s">
+        <v>289</v>
+      </c>
+      <c r="C10" t="s">
+        <v>93</v>
+      </c>
+      <c r="D10" t="s">
+        <v>94</v>
+      </c>
+      <c r="F10" t="s">
+        <v>281</v>
+      </c>
+      <c r="G10">
+        <v>100</v>
+      </c>
+      <c r="H10" t="s">
+        <v>334</v>
+      </c>
+      <c r="I10" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="11" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B11" t="s">
+        <v>289</v>
+      </c>
+      <c r="C11" t="s">
+        <v>95</v>
+      </c>
+      <c r="F11" t="s">
+        <v>281</v>
+      </c>
+      <c r="G11">
+        <v>65</v>
+      </c>
+      <c r="H11" t="s">
+        <v>334</v>
+      </c>
+      <c r="I11" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="12" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B12" t="s">
+        <v>290</v>
+      </c>
+      <c r="C12" t="s">
+        <v>96</v>
+      </c>
+      <c r="F12" t="s">
+        <v>281</v>
+      </c>
+      <c r="G12">
+        <v>100</v>
+      </c>
+      <c r="H12" t="s">
+        <v>334</v>
+      </c>
+      <c r="I12" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="13" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B13" t="s">
+        <v>290</v>
+      </c>
+      <c r="C13" t="s">
+        <v>97</v>
+      </c>
+      <c r="F13" t="s">
+        <v>281</v>
+      </c>
+      <c r="G13">
+        <v>70</v>
+      </c>
+      <c r="H13" t="s">
+        <v>334</v>
+      </c>
+      <c r="I13" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="14" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B14" t="s">
+        <v>290</v>
+      </c>
+      <c r="C14" t="s">
+        <v>98</v>
+      </c>
+      <c r="F14" t="s">
+        <v>281</v>
+      </c>
+      <c r="G14">
+        <v>70</v>
+      </c>
+      <c r="H14" t="s">
+        <v>334</v>
+      </c>
+      <c r="I14" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="15" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B15" t="s">
+        <v>290</v>
+      </c>
+      <c r="C15" t="s">
+        <v>99</v>
+      </c>
+      <c r="F15" t="s">
+        <v>281</v>
+      </c>
+      <c r="G15">
+        <v>70</v>
+      </c>
+      <c r="H15" t="s">
+        <v>334</v>
+      </c>
+      <c r="I15" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="16" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B16" t="s">
+        <v>290</v>
+      </c>
+      <c r="C16" t="s">
+        <v>100</v>
+      </c>
+      <c r="F16" t="s">
+        <v>281</v>
+      </c>
+      <c r="G16">
+        <v>80</v>
+      </c>
+      <c r="H16" t="s">
+        <v>334</v>
+      </c>
+      <c r="I16" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="17" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B17" t="s">
+        <v>290</v>
+      </c>
+      <c r="C17" t="s">
+        <v>101</v>
+      </c>
+      <c r="F17" t="s">
+        <v>281</v>
+      </c>
+      <c r="G17">
+        <v>190</v>
+      </c>
+      <c r="H17" t="s">
+        <v>334</v>
+      </c>
+      <c r="I17" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="18" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B18" t="s">
+        <v>290</v>
+      </c>
+      <c r="C18" t="s">
+        <v>102</v>
+      </c>
+      <c r="E18" t="s">
+        <v>326</v>
+      </c>
+      <c r="F18" t="s">
+        <v>281</v>
+      </c>
+      <c r="G18">
+        <v>100</v>
+      </c>
+      <c r="H18" t="s">
+        <v>334</v>
+      </c>
+      <c r="I18" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="19" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B19" t="s">
+        <v>291</v>
+      </c>
+      <c r="C19" t="s">
+        <v>103</v>
+      </c>
+      <c r="E19" t="s">
+        <v>285</v>
+      </c>
+      <c r="F19" t="s">
+        <v>281</v>
+      </c>
+      <c r="G19">
+        <v>150</v>
+      </c>
+      <c r="H19" t="s">
+        <v>334</v>
+      </c>
+      <c r="I19" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="20" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B20" t="s">
+        <v>292</v>
+      </c>
+      <c r="C20" t="s">
+        <v>104</v>
+      </c>
+      <c r="E20" t="s">
+        <v>107</v>
+      </c>
+      <c r="F20" t="s">
+        <v>281</v>
+      </c>
+      <c r="G20">
+        <v>110</v>
+      </c>
+      <c r="H20" t="s">
+        <v>334</v>
+      </c>
+      <c r="I20" t="s">
+        <v>338</v>
+      </c>
+      <c r="J20" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="21" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B21" t="s">
+        <v>293</v>
+      </c>
+      <c r="C21" t="s">
+        <v>294</v>
+      </c>
+      <c r="D21" t="s">
+        <v>105</v>
+      </c>
+      <c r="F21" t="s">
+        <v>281</v>
+      </c>
+      <c r="G21">
+        <v>65</v>
+      </c>
+      <c r="H21" t="s">
+        <v>334</v>
+      </c>
+      <c r="I21" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="22" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B22" t="s">
+        <v>293</v>
+      </c>
+      <c r="C22" t="s">
+        <v>295</v>
+      </c>
+      <c r="D22" t="s">
+        <v>106</v>
+      </c>
+      <c r="F22" t="s">
+        <v>281</v>
+      </c>
+      <c r="G22">
+        <v>85</v>
+      </c>
+      <c r="H22" t="s">
+        <v>334</v>
+      </c>
+      <c r="I22" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="23" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B23" t="s">
+        <v>282</v>
+      </c>
+      <c r="C23" t="s">
+        <v>119</v>
+      </c>
+      <c r="D23" t="s">
+        <v>120</v>
+      </c>
+      <c r="F23" t="s">
+        <v>316</v>
+      </c>
+      <c r="G23">
+        <v>100</v>
+      </c>
+      <c r="H23" t="s">
+        <v>334</v>
+      </c>
+      <c r="I23" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="24" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B24" t="s">
+        <v>282</v>
+      </c>
+      <c r="C24" t="s">
+        <v>54</v>
+      </c>
+      <c r="D24" t="s">
+        <v>121</v>
+      </c>
+      <c r="F24" t="s">
+        <v>316</v>
+      </c>
+      <c r="G24">
+        <v>100</v>
+      </c>
+      <c r="H24" t="s">
+        <v>334</v>
+      </c>
+      <c r="I24" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="25" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B25" t="s">
+        <v>282</v>
+      </c>
+      <c r="C25" t="s">
+        <v>33</v>
+      </c>
+      <c r="D25" t="s">
+        <v>122</v>
+      </c>
+      <c r="F25" t="s">
+        <v>316</v>
+      </c>
+      <c r="G25">
+        <v>100</v>
+      </c>
+      <c r="H25" t="s">
+        <v>334</v>
+      </c>
+      <c r="I25" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="26" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B26" t="s">
+        <v>282</v>
+      </c>
+      <c r="C26" t="s">
+        <v>42</v>
+      </c>
+      <c r="D26" t="s">
+        <v>123</v>
+      </c>
+      <c r="F26" t="s">
+        <v>316</v>
+      </c>
+      <c r="G26">
+        <v>100</v>
+      </c>
+      <c r="H26" t="s">
+        <v>334</v>
+      </c>
+      <c r="I26" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="27" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B27" t="s">
+        <v>282</v>
+      </c>
+      <c r="C27" t="s">
+        <v>124</v>
+      </c>
+      <c r="D27" t="s">
+        <v>125</v>
+      </c>
+      <c r="F27" t="s">
+        <v>316</v>
+      </c>
+      <c r="G27">
+        <v>100</v>
+      </c>
+      <c r="H27" t="s">
+        <v>334</v>
+      </c>
+      <c r="I27" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="28" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B28" t="s">
+        <v>282</v>
+      </c>
+      <c r="C28" t="s">
+        <v>126</v>
+      </c>
+      <c r="F28" t="s">
+        <v>316</v>
+      </c>
+      <c r="G28">
+        <v>100</v>
+      </c>
+      <c r="H28" t="s">
+        <v>334</v>
+      </c>
+      <c r="I28" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="29" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B29" t="s">
+        <v>282</v>
+      </c>
+      <c r="C29" t="s">
+        <v>10</v>
+      </c>
+      <c r="D29" t="s">
+        <v>127</v>
+      </c>
+      <c r="F29" t="s">
+        <v>316</v>
+      </c>
+      <c r="G29">
+        <v>110</v>
+      </c>
+      <c r="H29" t="s">
+        <v>334</v>
+      </c>
+      <c r="I29" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="30" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B30" t="s">
+        <v>128</v>
+      </c>
+      <c r="C30" t="s">
+        <v>131</v>
+      </c>
+      <c r="D30" t="s">
+        <v>129</v>
+      </c>
+      <c r="F30" t="s">
+        <v>316</v>
+      </c>
+      <c r="G30">
+        <v>105</v>
+      </c>
+      <c r="H30" t="s">
+        <v>334</v>
+      </c>
+      <c r="I30" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="31" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B31" t="s">
+        <v>128</v>
+      </c>
+      <c r="C31" t="s">
+        <v>130</v>
+      </c>
+      <c r="D31" t="s">
+        <v>129</v>
+      </c>
+      <c r="F31" t="s">
+        <v>316</v>
+      </c>
+      <c r="G31">
+        <v>105</v>
+      </c>
+      <c r="H31" t="s">
+        <v>334</v>
+      </c>
+      <c r="I31" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="32" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B32" t="s">
+        <v>128</v>
+      </c>
+      <c r="C32" t="s">
+        <v>132</v>
+      </c>
+      <c r="D32" t="s">
+        <v>133</v>
+      </c>
+      <c r="F32" t="s">
+        <v>316</v>
+      </c>
+      <c r="G32">
+        <v>105</v>
+      </c>
+      <c r="H32" t="s">
+        <v>334</v>
+      </c>
+      <c r="I32" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="33" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B33" t="s">
+        <v>128</v>
+      </c>
+      <c r="C33" t="s">
+        <v>134</v>
+      </c>
+      <c r="D33" t="s">
+        <v>135</v>
+      </c>
+      <c r="F33" t="s">
+        <v>316</v>
+      </c>
+      <c r="G33">
+        <v>105</v>
+      </c>
+      <c r="H33" t="s">
+        <v>334</v>
+      </c>
+      <c r="I33" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="34" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B34" t="s">
+        <v>128</v>
+      </c>
+      <c r="C34" t="s">
+        <v>12</v>
+      </c>
+      <c r="D34" t="s">
+        <v>136</v>
+      </c>
+      <c r="F34" t="s">
+        <v>316</v>
+      </c>
+      <c r="G34">
+        <v>105</v>
+      </c>
+      <c r="H34" t="s">
+        <v>334</v>
+      </c>
+      <c r="I34" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="35" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B35" t="s">
+        <v>128</v>
+      </c>
+      <c r="C35" t="s">
+        <v>6</v>
+      </c>
+      <c r="D35" t="s">
+        <v>137</v>
+      </c>
+      <c r="F35" t="s">
+        <v>316</v>
+      </c>
+      <c r="G35">
+        <v>105</v>
+      </c>
+      <c r="H35" t="s">
+        <v>334</v>
+      </c>
+      <c r="I35" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="36" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B36" t="s">
+        <v>138</v>
+      </c>
+      <c r="C36" t="s">
+        <v>139</v>
+      </c>
+      <c r="D36" t="s">
+        <v>140</v>
+      </c>
+      <c r="F36" t="s">
+        <v>316</v>
+      </c>
+      <c r="G36">
+        <v>95</v>
+      </c>
+      <c r="H36" t="s">
+        <v>334</v>
+      </c>
+      <c r="I36" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="37" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B37" t="s">
+        <v>138</v>
+      </c>
+      <c r="C37" t="s">
+        <v>141</v>
+      </c>
+      <c r="D37" t="s">
+        <v>142</v>
+      </c>
+      <c r="F37" t="s">
+        <v>316</v>
+      </c>
+      <c r="G37">
+        <v>85</v>
+      </c>
+      <c r="H37" t="s">
+        <v>334</v>
+      </c>
+      <c r="I37" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="38" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B38" t="s">
+        <v>209</v>
+      </c>
+      <c r="C38" t="s">
+        <v>210</v>
+      </c>
+      <c r="D38" t="s">
+        <v>211</v>
+      </c>
+      <c r="F38" t="s">
+        <v>316</v>
+      </c>
+      <c r="G38">
+        <v>100</v>
+      </c>
+      <c r="H38" t="s">
+        <v>334</v>
+      </c>
+      <c r="I38" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="39" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B39" t="s">
+        <v>209</v>
+      </c>
+      <c r="C39" t="s">
+        <v>212</v>
+      </c>
+      <c r="D39" t="s">
+        <v>213</v>
+      </c>
+      <c r="F39" t="s">
+        <v>316</v>
+      </c>
+      <c r="G39">
+        <v>100</v>
+      </c>
+      <c r="H39" t="s">
+        <v>334</v>
+      </c>
+      <c r="I39" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="40" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B40" t="s">
+        <v>209</v>
+      </c>
+      <c r="C40" t="s">
+        <v>214</v>
+      </c>
+      <c r="D40" t="s">
+        <v>215</v>
+      </c>
+      <c r="F40" t="s">
+        <v>316</v>
+      </c>
+      <c r="G40">
+        <v>100</v>
+      </c>
+      <c r="H40" t="s">
+        <v>334</v>
+      </c>
+      <c r="I40" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="41" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B41" t="s">
+        <v>209</v>
+      </c>
+      <c r="C41" t="s">
+        <v>216</v>
+      </c>
+      <c r="D41" t="s">
+        <v>217</v>
+      </c>
+      <c r="F41" t="s">
+        <v>316</v>
+      </c>
+      <c r="G41">
+        <v>100</v>
+      </c>
+      <c r="H41" t="s">
+        <v>334</v>
+      </c>
+      <c r="I41" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="42" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B42" t="s">
+        <v>209</v>
+      </c>
+      <c r="C42" t="s">
+        <v>218</v>
+      </c>
+      <c r="D42" t="s">
+        <v>219</v>
+      </c>
+      <c r="F42" t="s">
+        <v>316</v>
+      </c>
+      <c r="G42">
+        <v>100</v>
+      </c>
+      <c r="H42" t="s">
+        <v>334</v>
+      </c>
+      <c r="I42" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="43" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B43" t="s">
+        <v>153</v>
+      </c>
+      <c r="C43" t="s">
+        <v>311</v>
+      </c>
+      <c r="D43" t="s">
+        <v>143</v>
+      </c>
+      <c r="F43" t="s">
+        <v>281</v>
+      </c>
+      <c r="G43">
+        <v>140</v>
+      </c>
+      <c r="H43" t="s">
+        <v>334</v>
+      </c>
+      <c r="I43" t="s">
+        <v>338</v>
+      </c>
+      <c r="J43" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="44" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B44" t="s">
+        <v>153</v>
+      </c>
+      <c r="C44" t="s">
+        <v>312</v>
+      </c>
+      <c r="D44" t="s">
+        <v>144</v>
+      </c>
+      <c r="F44" t="s">
+        <v>281</v>
+      </c>
+      <c r="G44">
+        <v>140</v>
+      </c>
+      <c r="H44" t="s">
+        <v>334</v>
+      </c>
+      <c r="I44" t="s">
+        <v>338</v>
+      </c>
+      <c r="J44" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="45" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B45" t="s">
+        <v>153</v>
+      </c>
+      <c r="C45" t="s">
+        <v>312</v>
+      </c>
+      <c r="D45" t="s">
+        <v>145</v>
+      </c>
+      <c r="F45" t="s">
+        <v>281</v>
+      </c>
+      <c r="G45">
+        <v>180</v>
+      </c>
+      <c r="H45" t="s">
+        <v>334</v>
+      </c>
+      <c r="I45" t="s">
+        <v>338</v>
+      </c>
+      <c r="J45" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="46" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B46" t="s">
+        <v>153</v>
+      </c>
+      <c r="C46" t="s">
+        <v>146</v>
+      </c>
+      <c r="F46" t="s">
+        <v>281</v>
+      </c>
+      <c r="G46">
+        <v>140</v>
+      </c>
+      <c r="H46" t="s">
+        <v>334</v>
+      </c>
+      <c r="I46" t="s">
+        <v>338</v>
+      </c>
+      <c r="J46" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="47" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B47" t="s">
+        <v>153</v>
+      </c>
+      <c r="C47" t="s">
+        <v>313</v>
+      </c>
+      <c r="D47" t="s">
+        <v>144</v>
+      </c>
+      <c r="F47" t="s">
+        <v>281</v>
+      </c>
+      <c r="G47">
+        <v>140</v>
+      </c>
+      <c r="H47" t="s">
+        <v>334</v>
+      </c>
+      <c r="I47" t="s">
+        <v>338</v>
+      </c>
+      <c r="J47" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="48" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B48" t="s">
+        <v>153</v>
+      </c>
+      <c r="C48" t="s">
+        <v>313</v>
+      </c>
+      <c r="D48" t="s">
+        <v>145</v>
+      </c>
+      <c r="F48" t="s">
+        <v>281</v>
+      </c>
+      <c r="G48">
+        <v>180</v>
+      </c>
+      <c r="H48" t="s">
+        <v>334</v>
+      </c>
+      <c r="I48" t="s">
+        <v>338</v>
+      </c>
+      <c r="J48" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="49" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B49" t="s">
+        <v>153</v>
+      </c>
+      <c r="C49" t="s">
+        <v>147</v>
+      </c>
+      <c r="F49" t="s">
+        <v>281</v>
+      </c>
+      <c r="G49">
+        <v>140</v>
+      </c>
+      <c r="H49" t="s">
+        <v>334</v>
+      </c>
+      <c r="I49" t="s">
+        <v>338</v>
+      </c>
+      <c r="J49" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="50" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B50" t="s">
+        <v>314</v>
+      </c>
+      <c r="C50" t="s">
+        <v>150</v>
+      </c>
+      <c r="D50" t="s">
+        <v>151</v>
+      </c>
+      <c r="F50" t="s">
+        <v>281</v>
+      </c>
+      <c r="G50">
+        <v>130</v>
+      </c>
+      <c r="H50" t="s">
+        <v>334</v>
+      </c>
+      <c r="I50" t="s">
+        <v>338</v>
+      </c>
+      <c r="J50" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="51" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B51" t="s">
+        <v>152</v>
+      </c>
+      <c r="C51" t="s">
+        <v>154</v>
+      </c>
+      <c r="D51" t="s">
+        <v>155</v>
+      </c>
+      <c r="F51" t="s">
+        <v>281</v>
+      </c>
+      <c r="G51">
+        <v>110</v>
+      </c>
+      <c r="H51" t="s">
+        <v>334</v>
+      </c>
+      <c r="I51" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="52" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B52" t="s">
+        <v>152</v>
+      </c>
+      <c r="C52" t="s">
+        <v>156</v>
+      </c>
+      <c r="D52" t="s">
+        <v>157</v>
+      </c>
+      <c r="F52" t="s">
+        <v>281</v>
+      </c>
+      <c r="G52">
+        <v>110</v>
+      </c>
+      <c r="H52" t="s">
+        <v>334</v>
+      </c>
+      <c r="I52" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="53" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B53" t="s">
+        <v>152</v>
+      </c>
+      <c r="C53" t="s">
+        <v>158</v>
+      </c>
+      <c r="D53" t="s">
+        <v>160</v>
+      </c>
+      <c r="F53" t="s">
+        <v>281</v>
+      </c>
+      <c r="G53">
+        <v>120</v>
+      </c>
+      <c r="H53" t="s">
+        <v>334</v>
+      </c>
+      <c r="I53" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="54" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B54" t="s">
+        <v>152</v>
+      </c>
+      <c r="C54" t="s">
+        <v>159</v>
+      </c>
+      <c r="D54" t="s">
+        <v>161</v>
+      </c>
+      <c r="F54" t="s">
+        <v>281</v>
+      </c>
+      <c r="G54">
+        <v>120</v>
+      </c>
+      <c r="H54" t="s">
+        <v>334</v>
+      </c>
+      <c r="I54" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="55" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B55" t="s">
+        <v>152</v>
+      </c>
+      <c r="C55" t="s">
+        <v>162</v>
+      </c>
+      <c r="D55" t="s">
+        <v>163</v>
+      </c>
+      <c r="F55" t="s">
+        <v>281</v>
+      </c>
+      <c r="G55">
+        <v>120</v>
+      </c>
+      <c r="H55" t="s">
+        <v>334</v>
+      </c>
+      <c r="I55" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="56" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B56" t="s">
+        <v>152</v>
+      </c>
+      <c r="C56" t="s">
+        <v>164</v>
+      </c>
+      <c r="D56" t="s">
+        <v>165</v>
+      </c>
+      <c r="F56" t="s">
+        <v>281</v>
+      </c>
+      <c r="G56">
+        <v>120</v>
+      </c>
+      <c r="H56" t="s">
+        <v>334</v>
+      </c>
+      <c r="I56" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="57" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B57" t="s">
+        <v>221</v>
+      </c>
+      <c r="C57" t="s">
+        <v>222</v>
+      </c>
+      <c r="D57" t="s">
+        <v>223</v>
+      </c>
+      <c r="F57" t="s">
+        <v>242</v>
+      </c>
+      <c r="G57">
+        <v>85</v>
+      </c>
+      <c r="H57" t="s">
+        <v>334</v>
+      </c>
+      <c r="I57" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="58" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B58" t="s">
+        <v>221</v>
+      </c>
+      <c r="C58" t="s">
+        <v>222</v>
+      </c>
+      <c r="D58" t="s">
+        <v>223</v>
+      </c>
+      <c r="F58" t="s">
+        <v>29</v>
+      </c>
+      <c r="G58">
+        <v>100</v>
+      </c>
+      <c r="H58" t="s">
+        <v>334</v>
+      </c>
+      <c r="I58" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="59" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B59" t="s">
+        <v>221</v>
+      </c>
+      <c r="C59" t="s">
+        <v>224</v>
+      </c>
+      <c r="D59" t="s">
+        <v>225</v>
+      </c>
+      <c r="F59" t="s">
+        <v>242</v>
+      </c>
+      <c r="G59">
+        <v>85</v>
+      </c>
+      <c r="H59" t="s">
+        <v>334</v>
+      </c>
+      <c r="I59" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="60" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B60" t="s">
+        <v>221</v>
+      </c>
+      <c r="C60" t="s">
+        <v>224</v>
+      </c>
+      <c r="D60" t="s">
+        <v>225</v>
+      </c>
+      <c r="F60" t="s">
+        <v>29</v>
+      </c>
+      <c r="G60">
+        <v>100</v>
+      </c>
+      <c r="H60" t="s">
+        <v>334</v>
+      </c>
+      <c r="I60" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="61" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B61" t="s">
+        <v>221</v>
+      </c>
+      <c r="C61" t="s">
+        <v>226</v>
+      </c>
+      <c r="D61" t="s">
+        <v>227</v>
+      </c>
+      <c r="F61" t="s">
+        <v>242</v>
+      </c>
+      <c r="G61">
+        <v>85</v>
+      </c>
+      <c r="H61" t="s">
+        <v>334</v>
+      </c>
+      <c r="I61" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="62" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B62" t="s">
+        <v>221</v>
+      </c>
+      <c r="C62" t="s">
+        <v>226</v>
+      </c>
+      <c r="D62" t="s">
+        <v>227</v>
+      </c>
+      <c r="F62" t="s">
+        <v>29</v>
+      </c>
+      <c r="G62">
+        <v>100</v>
+      </c>
+      <c r="H62" t="s">
+        <v>334</v>
+      </c>
+      <c r="I62" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="63" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B63" t="s">
+        <v>221</v>
+      </c>
+      <c r="C63" t="s">
+        <v>228</v>
+      </c>
+      <c r="D63" t="s">
+        <v>229</v>
+      </c>
+      <c r="F63" t="s">
+        <v>242</v>
+      </c>
+      <c r="G63">
+        <v>85</v>
+      </c>
+      <c r="H63" t="s">
+        <v>334</v>
+      </c>
+      <c r="I63" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="64" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B64" t="s">
+        <v>221</v>
+      </c>
+      <c r="C64" t="s">
+        <v>228</v>
+      </c>
+      <c r="D64" t="s">
+        <v>229</v>
+      </c>
+      <c r="F64" t="s">
+        <v>29</v>
+      </c>
+      <c r="G64">
+        <v>100</v>
+      </c>
+      <c r="H64" t="s">
+        <v>334</v>
+      </c>
+      <c r="I64" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="65" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B65" t="s">
+        <v>221</v>
+      </c>
+      <c r="C65" t="s">
+        <v>230</v>
+      </c>
+      <c r="D65" t="s">
+        <v>231</v>
+      </c>
+      <c r="F65" t="s">
+        <v>242</v>
+      </c>
+      <c r="G65">
+        <v>85</v>
+      </c>
+      <c r="H65" t="s">
+        <v>334</v>
+      </c>
+      <c r="I65" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="66" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B66" t="s">
+        <v>221</v>
+      </c>
+      <c r="C66" t="s">
+        <v>230</v>
+      </c>
+      <c r="D66" t="s">
+        <v>231</v>
+      </c>
+      <c r="F66" t="s">
+        <v>29</v>
+      </c>
+      <c r="G66">
+        <v>100</v>
+      </c>
+      <c r="H66" t="s">
+        <v>334</v>
+      </c>
+      <c r="I66" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="67" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B67" t="s">
+        <v>221</v>
+      </c>
+      <c r="C67" t="s">
+        <v>232</v>
+      </c>
+      <c r="D67" t="s">
+        <v>233</v>
+      </c>
+      <c r="F67" t="s">
+        <v>242</v>
+      </c>
+      <c r="G67">
+        <v>85</v>
+      </c>
+      <c r="H67" t="s">
+        <v>334</v>
+      </c>
+      <c r="I67" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="68" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B68" t="s">
+        <v>221</v>
+      </c>
+      <c r="C68" t="s">
+        <v>232</v>
+      </c>
+      <c r="D68" t="s">
+        <v>233</v>
+      </c>
+      <c r="F68" t="s">
+        <v>29</v>
+      </c>
+      <c r="G68">
+        <v>100</v>
+      </c>
+      <c r="H68" t="s">
+        <v>334</v>
+      </c>
+      <c r="I68" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="69" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B69" t="s">
+        <v>221</v>
+      </c>
+      <c r="C69" t="s">
+        <v>234</v>
+      </c>
+      <c r="D69" t="s">
+        <v>235</v>
+      </c>
+      <c r="F69" t="s">
+        <v>242</v>
+      </c>
+      <c r="G69">
+        <v>85</v>
+      </c>
+      <c r="H69" t="s">
+        <v>334</v>
+      </c>
+      <c r="I69" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="70" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B70" t="s">
+        <v>221</v>
+      </c>
+      <c r="C70" t="s">
+        <v>234</v>
+      </c>
+      <c r="D70" t="s">
+        <v>235</v>
+      </c>
+      <c r="F70" t="s">
+        <v>29</v>
+      </c>
+      <c r="G70">
+        <v>100</v>
+      </c>
+      <c r="H70" t="s">
+        <v>334</v>
+      </c>
+      <c r="I70" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="71" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B71" t="s">
+        <v>221</v>
+      </c>
+      <c r="C71" t="s">
+        <v>236</v>
+      </c>
+      <c r="D71" t="s">
+        <v>237</v>
+      </c>
+      <c r="F71" t="s">
+        <v>242</v>
+      </c>
+      <c r="G71">
+        <v>85</v>
+      </c>
+      <c r="H71" t="s">
+        <v>334</v>
+      </c>
+      <c r="I71" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="72" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B72" t="s">
+        <v>221</v>
+      </c>
+      <c r="C72" t="s">
+        <v>236</v>
+      </c>
+      <c r="D72" t="s">
+        <v>237</v>
+      </c>
+      <c r="F72" t="s">
+        <v>29</v>
+      </c>
+      <c r="G72">
+        <v>100</v>
+      </c>
+      <c r="H72" t="s">
+        <v>334</v>
+      </c>
+      <c r="I72" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="73" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B73" t="s">
+        <v>240</v>
+      </c>
+      <c r="C73" t="s">
+        <v>247</v>
+      </c>
+      <c r="D73" t="s">
+        <v>241</v>
+      </c>
+      <c r="F73" t="s">
+        <v>242</v>
+      </c>
+      <c r="G73">
+        <v>90</v>
+      </c>
+      <c r="H73" t="s">
+        <v>334</v>
+      </c>
+      <c r="I73" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="74" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B74" t="s">
+        <v>240</v>
+      </c>
+      <c r="C74" t="s">
+        <v>247</v>
+      </c>
+      <c r="D74" t="s">
+        <v>241</v>
+      </c>
+      <c r="F74" t="s">
+        <v>29</v>
+      </c>
+      <c r="G74">
+        <v>110</v>
+      </c>
+      <c r="H74" t="s">
+        <v>334</v>
+      </c>
+      <c r="I74" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="75" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B75" t="s">
+        <v>240</v>
+      </c>
+      <c r="C75" t="s">
+        <v>243</v>
+      </c>
+      <c r="D75" t="s">
+        <v>244</v>
+      </c>
+      <c r="F75" t="s">
+        <v>242</v>
+      </c>
+      <c r="G75">
+        <v>90</v>
+      </c>
+      <c r="H75" t="s">
+        <v>334</v>
+      </c>
+      <c r="I75" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="76" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B76" t="s">
+        <v>240</v>
+      </c>
+      <c r="C76" t="s">
+        <v>243</v>
+      </c>
+      <c r="D76" t="s">
+        <v>244</v>
+      </c>
+      <c r="F76" t="s">
+        <v>29</v>
+      </c>
+      <c r="G76">
+        <v>110</v>
+      </c>
+      <c r="H76" t="s">
+        <v>334</v>
+      </c>
+      <c r="I76" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="77" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B77" t="s">
+        <v>245</v>
+      </c>
+      <c r="C77" t="s">
+        <v>246</v>
+      </c>
+      <c r="D77" t="s">
+        <v>249</v>
+      </c>
+      <c r="E77" t="s">
+        <v>248</v>
+      </c>
+      <c r="F77" t="s">
+        <v>242</v>
+      </c>
+      <c r="G77">
+        <v>90</v>
+      </c>
+      <c r="H77" t="s">
+        <v>334</v>
+      </c>
+      <c r="I77" t="s">
+        <v>338</v>
+      </c>
+      <c r="J77" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="78" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B78" t="s">
+        <v>245</v>
+      </c>
+      <c r="C78" t="s">
+        <v>246</v>
+      </c>
+      <c r="D78" t="s">
+        <v>250</v>
+      </c>
+      <c r="E78" t="s">
+        <v>248</v>
+      </c>
+      <c r="F78" t="s">
+        <v>29</v>
+      </c>
+      <c r="G78">
+        <v>110</v>
+      </c>
+      <c r="H78" t="s">
+        <v>334</v>
+      </c>
+      <c r="I78" t="s">
+        <v>338</v>
+      </c>
+      <c r="J78" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="79" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B79" t="s">
+        <v>238</v>
+      </c>
+      <c r="C79" t="s">
+        <v>239</v>
+      </c>
+      <c r="D79" t="s">
+        <v>252</v>
+      </c>
+      <c r="F79" t="s">
+        <v>316</v>
+      </c>
+      <c r="G79">
+        <v>90</v>
+      </c>
+      <c r="H79" t="s">
+        <v>334</v>
+      </c>
+      <c r="I79" t="s">
+        <v>338</v>
+      </c>
+      <c r="J79" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="80" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B80" t="s">
+        <v>238</v>
+      </c>
+      <c r="C80" t="s">
+        <v>253</v>
+      </c>
+      <c r="D80" t="s">
+        <v>254</v>
+      </c>
+      <c r="F80" t="s">
+        <v>316</v>
+      </c>
+      <c r="G80">
+        <v>110</v>
+      </c>
+      <c r="H80" t="s">
+        <v>334</v>
+      </c>
+      <c r="I80" t="s">
+        <v>338</v>
+      </c>
+      <c r="J80" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="81" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B81" t="s">
+        <v>238</v>
+      </c>
+      <c r="C81" t="s">
+        <v>255</v>
+      </c>
+      <c r="D81" t="s">
+        <v>256</v>
+      </c>
+      <c r="F81" t="s">
+        <v>316</v>
+      </c>
+      <c r="G81">
+        <v>110</v>
+      </c>
+      <c r="H81" t="s">
+        <v>334</v>
+      </c>
+      <c r="I81" t="s">
+        <v>338</v>
+      </c>
+      <c r="J81" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="82" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B82" t="s">
+        <v>238</v>
+      </c>
+      <c r="C82" t="s">
+        <v>257</v>
+      </c>
+      <c r="D82" t="s">
+        <v>258</v>
+      </c>
+      <c r="F82" t="s">
+        <v>316</v>
+      </c>
+      <c r="G82">
+        <v>80</v>
+      </c>
+      <c r="H82" t="s">
+        <v>334</v>
+      </c>
+      <c r="I82" t="s">
+        <v>338</v>
+      </c>
+      <c r="J82" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="83" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B83" t="s">
+        <v>238</v>
+      </c>
+      <c r="C83" t="s">
+        <v>259</v>
+      </c>
+      <c r="D83" t="s">
+        <v>260</v>
+      </c>
+      <c r="F83" t="s">
+        <v>316</v>
+      </c>
+      <c r="G83">
+        <v>100</v>
+      </c>
+      <c r="H83" t="s">
+        <v>334</v>
+      </c>
+      <c r="I83" t="s">
+        <v>338</v>
+      </c>
+      <c r="J83" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="84" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B84" t="s">
+        <v>238</v>
+      </c>
+      <c r="C84" t="s">
+        <v>261</v>
+      </c>
+      <c r="D84" t="s">
+        <v>262</v>
+      </c>
+      <c r="E84" t="s">
+        <v>263</v>
+      </c>
+      <c r="F84" t="s">
+        <v>316</v>
+      </c>
+      <c r="G84">
+        <v>90</v>
+      </c>
+      <c r="H84" t="s">
+        <v>334</v>
+      </c>
+      <c r="I84" t="s">
+        <v>338</v>
+      </c>
+      <c r="J84" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="85" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B85" t="s">
+        <v>264</v>
+      </c>
+      <c r="C85" t="s">
+        <v>265</v>
+      </c>
+      <c r="F85" t="s">
+        <v>316</v>
+      </c>
+      <c r="G85">
+        <v>18</v>
+      </c>
+      <c r="H85" t="s">
+        <v>334</v>
+      </c>
+      <c r="I85" t="s">
+        <v>338</v>
+      </c>
+      <c r="J85" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="86" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B86" t="s">
+        <v>264</v>
+      </c>
+      <c r="C86" t="s">
+        <v>266</v>
+      </c>
+      <c r="F86" t="s">
+        <v>316</v>
+      </c>
+      <c r="G86">
+        <v>20</v>
+      </c>
+      <c r="H86" t="s">
+        <v>334</v>
+      </c>
+      <c r="I86" t="s">
+        <v>338</v>
+      </c>
+      <c r="J86" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="87" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B87" t="s">
+        <v>264</v>
+      </c>
+      <c r="C87" t="s">
+        <v>267</v>
+      </c>
+      <c r="F87" t="s">
+        <v>316</v>
+      </c>
+      <c r="G87">
+        <v>20</v>
+      </c>
+      <c r="H87" t="s">
+        <v>334</v>
+      </c>
+      <c r="I87" t="s">
+        <v>338</v>
+      </c>
+      <c r="J87" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="88" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B88" t="s">
+        <v>264</v>
+      </c>
+      <c r="C88" t="s">
+        <v>268</v>
+      </c>
+      <c r="F88" t="s">
+        <v>316</v>
+      </c>
+      <c r="G88">
+        <v>28</v>
+      </c>
+      <c r="H88" t="s">
+        <v>334</v>
+      </c>
+      <c r="I88" t="s">
+        <v>338</v>
+      </c>
+      <c r="J88" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="89" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B89" t="s">
+        <v>269</v>
+      </c>
+      <c r="C89" t="s">
+        <v>270</v>
+      </c>
+      <c r="D89" t="s">
+        <v>271</v>
+      </c>
+      <c r="E89" t="s">
+        <v>272</v>
+      </c>
+      <c r="F89" t="s">
+        <v>316</v>
+      </c>
+      <c r="G89">
+        <v>75</v>
+      </c>
+      <c r="H89" t="s">
+        <v>334</v>
+      </c>
+      <c r="I89" t="s">
+        <v>338</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="0" orientation="portrait" horizontalDpi="203" verticalDpi="203" r:id="rId1"/>
+  <tableParts count="1">
+    <tablePart r:id="rId2"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="B2:K6"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="11.5703125" customWidth="1"/>
+    <col min="3" max="3" width="14.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.42578125" customWidth="1"/>
+    <col min="5" max="5" width="85.28515625" customWidth="1"/>
+    <col min="8" max="8" width="18.85546875" customWidth="1"/>
+    <col min="9" max="9" width="21.28515625" customWidth="1"/>
+    <col min="10" max="10" width="17" customWidth="1"/>
+    <col min="11" max="11" width="17.5703125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B2" t="s">
+        <v>319</v>
+      </c>
+      <c r="C2" t="s">
+        <v>320</v>
+      </c>
+      <c r="D2" t="s">
+        <v>321</v>
+      </c>
+      <c r="E2" t="s">
+        <v>322</v>
+      </c>
+      <c r="F2" t="s">
+        <v>323</v>
+      </c>
+      <c r="G2" t="s">
+        <v>324</v>
+      </c>
+      <c r="H2" t="s">
+        <v>325</v>
+      </c>
+      <c r="I2" t="s">
+        <v>337</v>
+      </c>
+      <c r="J2" t="s">
+        <v>327</v>
+      </c>
+      <c r="K2" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="3" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B3" t="s">
+        <v>114</v>
+      </c>
+      <c r="C3" t="s">
+        <v>115</v>
+      </c>
+      <c r="E3" t="s">
+        <v>280</v>
+      </c>
+      <c r="F3" t="s">
+        <v>339</v>
+      </c>
+      <c r="G3">
+        <v>110</v>
+      </c>
+      <c r="H3" t="s">
+        <v>334</v>
+      </c>
+      <c r="I3" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="4" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B4" t="s">
+        <v>114</v>
+      </c>
+      <c r="C4" t="s">
+        <v>116</v>
+      </c>
+      <c r="E4" t="s">
+        <v>280</v>
+      </c>
+      <c r="F4" t="s">
+        <v>340</v>
+      </c>
+      <c r="G4">
+        <v>150</v>
+      </c>
+      <c r="H4" t="s">
+        <v>334</v>
+      </c>
+      <c r="I4" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="5" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B5" t="s">
+        <v>114</v>
+      </c>
+      <c r="C5" t="s">
+        <v>117</v>
+      </c>
+      <c r="E5" t="s">
+        <v>280</v>
+      </c>
+      <c r="F5" t="s">
+        <v>341</v>
+      </c>
+      <c r="G5">
+        <v>210</v>
+      </c>
+      <c r="H5" t="s">
+        <v>334</v>
+      </c>
+      <c r="I5" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="6" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B6" t="s">
+        <v>114</v>
+      </c>
+      <c r="C6" t="s">
+        <v>118</v>
+      </c>
+      <c r="E6" t="s">
+        <v>280</v>
+      </c>
+      <c r="F6" t="s">
+        <v>342</v>
+      </c>
+      <c r="G6">
+        <v>290</v>
+      </c>
+      <c r="H6" t="s">
+        <v>334</v>
+      </c>
+      <c r="I6" t="s">
+        <v>338</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="B2:K8"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="11.5703125" customWidth="1"/>
+    <col min="3" max="3" width="25.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.42578125" customWidth="1"/>
+    <col min="5" max="5" width="117.28515625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="18.140625" customWidth="1"/>
+    <col min="9" max="9" width="18.5703125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13.42578125" customWidth="1"/>
+    <col min="11" max="11" width="14.5703125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B2" t="s">
+        <v>319</v>
+      </c>
+      <c r="C2" t="s">
+        <v>320</v>
+      </c>
+      <c r="D2" t="s">
+        <v>321</v>
+      </c>
+      <c r="E2" t="s">
+        <v>322</v>
+      </c>
+      <c r="F2" t="s">
+        <v>323</v>
+      </c>
+      <c r="G2" t="s">
+        <v>324</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>337</v>
+      </c>
+      <c r="J2" t="s">
+        <v>327</v>
+      </c>
+      <c r="K2" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="3" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B3" t="s">
+        <v>108</v>
+      </c>
+      <c r="C3" t="s">
+        <v>109</v>
+      </c>
+      <c r="E3" t="s">
+        <v>357</v>
+      </c>
+      <c r="F3" t="s">
+        <v>316</v>
+      </c>
+      <c r="G3">
+        <v>80</v>
+      </c>
+      <c r="H3" t="s">
+        <v>334</v>
+      </c>
+      <c r="I3" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="4" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B4" t="s">
+        <v>108</v>
+      </c>
+      <c r="C4" t="s">
+        <v>274</v>
+      </c>
+      <c r="E4" t="s">
+        <v>275</v>
+      </c>
+      <c r="F4" t="s">
+        <v>316</v>
+      </c>
+      <c r="G4">
+        <v>85</v>
+      </c>
+      <c r="H4" t="s">
+        <v>334</v>
+      </c>
+      <c r="I4" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="5" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B5" t="s">
+        <v>108</v>
+      </c>
+      <c r="C5" t="s">
+        <v>110</v>
+      </c>
+      <c r="E5" t="s">
+        <v>276</v>
+      </c>
+      <c r="F5" t="s">
+        <v>316</v>
+      </c>
+      <c r="G5">
+        <v>50</v>
+      </c>
+      <c r="H5" t="s">
+        <v>334</v>
+      </c>
+      <c r="I5" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="6" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B6" t="s">
+        <v>108</v>
+      </c>
+      <c r="C6" t="s">
+        <v>111</v>
+      </c>
+      <c r="E6" t="s">
+        <v>277</v>
+      </c>
+      <c r="F6" t="s">
+        <v>316</v>
+      </c>
+      <c r="G6">
+        <v>50</v>
+      </c>
+      <c r="H6" t="s">
+        <v>334</v>
+      </c>
+      <c r="I6" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="7" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B7" t="s">
+        <v>108</v>
+      </c>
+      <c r="C7" t="s">
+        <v>112</v>
+      </c>
+      <c r="E7" t="s">
+        <v>278</v>
+      </c>
+      <c r="F7" t="s">
+        <v>316</v>
+      </c>
+      <c r="G7">
+        <v>80</v>
+      </c>
+      <c r="H7" t="s">
+        <v>334</v>
+      </c>
+      <c r="I7" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="8" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B8" t="s">
+        <v>108</v>
+      </c>
+      <c r="C8" t="s">
+        <v>113</v>
+      </c>
+      <c r="E8" t="s">
+        <v>279</v>
+      </c>
+      <c r="F8" t="s">
+        <v>316</v>
+      </c>
+      <c r="G8">
+        <v>60</v>
+      </c>
+      <c r="H8" t="s">
+        <v>334</v>
+      </c>
+      <c r="I8" t="s">
+        <v>92</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="B2:E21"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="3" width="23.28515625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B2" t="s">
+        <v>319</v>
+      </c>
+      <c r="C2" t="s">
+        <v>345</v>
+      </c>
+      <c r="D2" t="s">
+        <v>323</v>
+      </c>
+      <c r="E2" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="3" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B3" t="s">
+        <v>346</v>
+      </c>
+      <c r="C3" t="s">
+        <v>344</v>
+      </c>
+      <c r="D3" t="s">
+        <v>24</v>
+      </c>
+      <c r="E3">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="4" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B4" t="s">
+        <v>346</v>
+      </c>
+      <c r="C4" t="s">
+        <v>343</v>
+      </c>
+      <c r="D4" t="s">
+        <v>24</v>
+      </c>
+      <c r="E4">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="5" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B5" t="s">
+        <v>346</v>
+      </c>
+      <c r="C5" t="s">
+        <v>344</v>
+      </c>
+      <c r="D5" t="s">
+        <v>25</v>
+      </c>
+      <c r="E5">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="6" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B6" t="s">
+        <v>346</v>
+      </c>
+      <c r="C6" t="s">
+        <v>343</v>
+      </c>
+      <c r="D6" t="s">
+        <v>25</v>
+      </c>
+      <c r="E6">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="7" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B7" t="s">
+        <v>346</v>
+      </c>
+      <c r="C7" t="s">
+        <v>344</v>
+      </c>
+      <c r="D7" t="s">
+        <v>26</v>
+      </c>
+      <c r="E7">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="8" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B8" t="s">
+        <v>346</v>
+      </c>
+      <c r="C8" t="s">
+        <v>343</v>
+      </c>
+      <c r="D8" t="s">
+        <v>26</v>
+      </c>
+      <c r="E8">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="9" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B9" t="s">
+        <v>346</v>
+      </c>
+      <c r="C9" t="s">
+        <v>344</v>
+      </c>
+      <c r="D9" t="s">
+        <v>29</v>
+      </c>
+      <c r="E9">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="10" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B10" t="s">
+        <v>346</v>
+      </c>
+      <c r="C10" t="s">
+        <v>343</v>
+      </c>
+      <c r="D10" t="s">
+        <v>29</v>
+      </c>
+      <c r="E10">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="11" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B11" t="s">
+        <v>346</v>
+      </c>
+      <c r="C11" t="s">
+        <v>344</v>
+      </c>
+      <c r="D11" t="s">
+        <v>27</v>
+      </c>
+      <c r="E11">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="12" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B12" t="s">
+        <v>346</v>
+      </c>
+      <c r="C12" t="s">
+        <v>343</v>
+      </c>
+      <c r="D12" t="s">
+        <v>27</v>
+      </c>
+      <c r="E12">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="13" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B13" t="s">
+        <v>346</v>
+      </c>
+      <c r="C13" t="s">
+        <v>344</v>
+      </c>
+      <c r="D13" t="s">
+        <v>28</v>
+      </c>
+      <c r="E13">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="14" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B14" t="s">
+        <v>346</v>
+      </c>
+      <c r="C14" t="s">
+        <v>343</v>
+      </c>
+      <c r="D14" t="s">
+        <v>28</v>
+      </c>
+      <c r="E14">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="15" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B15" t="s">
+        <v>347</v>
+      </c>
+      <c r="C15" t="s">
+        <v>148</v>
+      </c>
+      <c r="D15" t="s">
+        <v>355</v>
+      </c>
+      <c r="E15">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="16" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B16" t="s">
+        <v>353</v>
+      </c>
+      <c r="C16" t="s">
+        <v>354</v>
+      </c>
+      <c r="D16" t="s">
+        <v>281</v>
+      </c>
+      <c r="E16">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="17" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B17" t="s">
+        <v>169</v>
+      </c>
+      <c r="C17" t="s">
+        <v>348</v>
+      </c>
+      <c r="D17" t="s">
+        <v>281</v>
+      </c>
+      <c r="E17">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="18" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B18" t="s">
+        <v>169</v>
+      </c>
+      <c r="C18" t="s">
+        <v>349</v>
+      </c>
+      <c r="D18" t="s">
+        <v>281</v>
+      </c>
+      <c r="E18">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="19" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B19" t="s">
+        <v>169</v>
+      </c>
+      <c r="C19" t="s">
+        <v>350</v>
+      </c>
+      <c r="D19" t="s">
+        <v>281</v>
+      </c>
+      <c r="E19">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="20" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B20" t="s">
+        <v>169</v>
+      </c>
+      <c r="C20" t="s">
+        <v>351</v>
+      </c>
+      <c r="D20" t="s">
+        <v>281</v>
+      </c>
+      <c r="E20">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="21" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B21" t="s">
+        <v>169</v>
+      </c>
+      <c r="C21" t="s">
+        <v>352</v>
+      </c>
+      <c r="D21" t="s">
+        <v>281</v>
+      </c>
+      <c r="E21">
+        <v>15</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>